--- a/oilSupplyNewsShocks_2025M12.xlsx
+++ b/oilSupplyNewsShocks_2025M12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/drk9452_ads_northwestern_edu/Documents/Uni/LBS PhD/Research/Projects/Oil supply shocks/Repositories/OilSupplyNewsUpdate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{4C726BAA-E1C5-418C-8B7A-95BF62D9CC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C67E17BD-88AB-4557-8B7E-7162EBB51F40}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{4C726BAA-E1C5-418C-8B7A-95BF62D9CC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{845A5F45-3AB2-4798-BFA4-20C1629A3C1C}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{2F60C053-7737-4149-ACD9-933D8ABD6E05}"/>
+    <workbookView xWindow="74520" yWindow="5400" windowWidth="6915" windowHeight="4080" firstSheet="3" activeTab="3" xr2:uid="{2F60C053-7737-4149-ACD9-933D8ABD6E05}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily (pre-Covid)" sheetId="5" r:id="rId1"/>
@@ -22106,7 +22106,7 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>-0.84431964900372047</v>
+        <v>-0.4104981705015856</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22117,7 +22117,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.74241800555894877</v>
+        <v>0.89610968014193249</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22128,7 +22128,7 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>-0.35374876460217963</v>
+        <v>-0.39723124124740633</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22139,7 +22139,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>-0.57574403255481965</v>
+        <v>-0.37189187160424614</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22150,7 +22150,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>2.5443996074666349E-3</v>
+        <v>-3.3306007510880725E-2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22161,7 +22161,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>6.7143607905833291E-2</v>
+        <v>0.19361928562177499</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22172,7 +22172,7 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>-2.0479136210716999E-3</v>
+        <v>-9.2466832452874612E-2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22183,7 +22183,7 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>-0.39326993565608925</v>
+        <v>-0.57216532889215632</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22194,7 +22194,7 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>-0.17734559738957492</v>
+        <v>-0.16667340422388491</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22205,7 +22205,7 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>-1.2642900396514649</v>
+        <v>-1.0127104218566778</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22216,7 +22216,7 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0.17622667434786901</v>
+        <v>1.5395152640865743E-2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22227,7 +22227,7 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>-0.5574798128427414</v>
+        <v>-0.2526767831377606</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22238,7 +22238,7 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>-0.37005044605679238</v>
+        <v>-0.10732475095275232</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22249,7 +22249,7 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0.17735394083249073</v>
+        <v>-0.13260493177256183</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22260,7 +22260,7 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>-0.33123156754373639</v>
+        <v>-0.61249882758092156</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22271,7 +22271,7 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>-0.2351730513605336</v>
+        <v>-0.5514230566309094</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22282,7 +22282,7 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>-0.43636007232434398</v>
+        <v>-0.87196943393398951</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22293,7 +22293,7 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0.58743557605864405</v>
+        <v>0.3031134118631818</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22304,7 +22304,7 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>-0.16397983097016086</v>
+        <v>-0.23821111670174561</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22315,7 +22315,7 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0.33246918065745878</v>
+        <v>0.29850597786906508</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22326,7 +22326,7 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>0.78034101680390511</v>
+        <v>0.58534032077135356</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22337,7 +22337,7 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>0.55254765177015963</v>
+        <v>0.33148823727450411</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22348,7 +22348,7 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>-0.29897369709043464</v>
+        <v>-0.53235470335585255</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22359,7 +22359,7 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>0.33440853206563032</v>
+        <v>0.2403283842040761</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22370,7 +22370,7 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>-0.23116871451559948</v>
+        <v>-0.12985297957696157</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22381,7 +22381,7 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.27743791398906265</v>
+        <v>0.14466312710305373</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22392,7 +22392,7 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>-0.69647877003750847</v>
+        <v>-0.59831484696896864</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22403,7 +22403,7 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>-0.16597502837949188</v>
+        <v>0.25540129388887017</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22414,7 +22414,7 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>-0.26829508669071089</v>
+        <v>0.12761247520566812</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22425,7 +22425,7 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>-0.45529829780686226</v>
+        <v>-0.1787258901206023</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22436,7 +22436,7 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>-2.31112636634529E-2</v>
+        <v>0.52167209769155376</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22447,7 +22447,7 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0.46985270304931026</v>
+        <v>0.47638745198858495</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22458,7 +22458,7 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>-9.7033533762986401E-2</v>
+        <v>-0.16755427321039482</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22469,7 +22469,7 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>-0.78995147383132192</v>
+        <v>-0.80535993873084388</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22480,7 +22480,7 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0.52015610293464709</v>
+        <v>0.68545957968582638</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22491,7 +22491,7 @@
         <v>0</v>
       </c>
       <c r="C37">
-        <v>-0.28382875820329001</v>
+        <v>-0.35157811747662088</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22502,7 +22502,7 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>-2.9448824743157003E-2</v>
+        <v>7.9134307893977629E-2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22513,7 +22513,7 @@
         <v>0</v>
       </c>
       <c r="C39">
-        <v>-0.61972241744698309</v>
+        <v>-0.79642706109800998</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22524,7 +22524,7 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>-0.38255260783813583</v>
+        <v>-0.1633544381486593</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22535,7 +22535,7 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>-0.38137989552370954</v>
+        <v>-0.55994117026525048</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22546,7 +22546,7 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>-0.21495578979609756</v>
+        <v>-0.19347313721796267</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22557,7 +22557,7 @@
         <v>0</v>
       </c>
       <c r="C43">
-        <v>-4.1776645947164716E-2</v>
+        <v>1.3568991998547972E-2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22568,7 +22568,7 @@
         <v>0</v>
       </c>
       <c r="C44">
-        <v>0.25659146903714836</v>
+        <v>0.50128224645756747</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22579,7 +22579,7 @@
         <v>0</v>
       </c>
       <c r="C45">
-        <v>-0.49473282295423193</v>
+        <v>-0.6882960762336201</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22590,7 +22590,7 @@
         <v>0</v>
       </c>
       <c r="C46">
-        <v>0.71983297923735134</v>
+        <v>0.4596064333049551</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22601,7 +22601,7 @@
         <v>0</v>
       </c>
       <c r="C47">
-        <v>6.5393942905813435E-2</v>
+        <v>-0.12802686272737784</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22612,7 +22612,7 @@
         <v>0</v>
       </c>
       <c r="C48">
-        <v>-0.44414419784204251</v>
+        <v>-0.40721436171559316</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22623,7 +22623,7 @@
         <v>0</v>
       </c>
       <c r="C49">
-        <v>-0.44080146033611955</v>
+        <v>-0.44832038822103082</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22634,7 +22634,7 @@
         <v>0</v>
       </c>
       <c r="C50">
-        <v>0.2165228085501881</v>
+        <v>0.18986754801023936</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22645,7 +22645,7 @@
         <v>0</v>
       </c>
       <c r="C51">
-        <v>0.28638879301899284</v>
+        <v>0.35237114746624493</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22656,7 +22656,7 @@
         <v>0</v>
       </c>
       <c r="C52">
-        <v>5.9764322599799767E-2</v>
+        <v>-8.3816753568336816E-2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22667,7 +22667,7 @@
         <v>0</v>
       </c>
       <c r="C53">
-        <v>0.66890542730512192</v>
+        <v>0.31174885723418871</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22678,7 +22678,7 @@
         <v>0</v>
       </c>
       <c r="C54">
-        <v>0.32955691373744617</v>
+        <v>0.11219379494526376</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22689,7 +22689,7 @@
         <v>0</v>
       </c>
       <c r="C55">
-        <v>0.87058769023370219</v>
+        <v>0.96051327856428437</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="C56">
-        <v>1.1209017443156737</v>
+        <v>0.81655228765139931</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22711,7 +22711,7 @@
         <v>0</v>
       </c>
       <c r="C57">
-        <v>1.0925302458978703</v>
+        <v>1.1254247157408666</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22722,7 +22722,7 @@
         <v>0</v>
       </c>
       <c r="C58">
-        <v>0.64748550645078873</v>
+        <v>0.29404298417440894</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22733,7 +22733,7 @@
         <v>0</v>
       </c>
       <c r="C59">
-        <v>0.10461762565796899</v>
+        <v>0.37138933575956068</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22744,7 +22744,7 @@
         <v>0</v>
       </c>
       <c r="C60">
-        <v>0.9309917134956267</v>
+        <v>0.52379086430715605</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22755,7 +22755,7 @@
         <v>0</v>
       </c>
       <c r="C61">
-        <v>0.40079335153738532</v>
+        <v>0.49430035876577488</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22766,7 +22766,7 @@
         <v>0</v>
       </c>
       <c r="C62">
-        <v>2.716501203309616E-2</v>
+        <v>7.2688902215996165E-2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22777,7 +22777,7 @@
         <v>0</v>
       </c>
       <c r="C63">
-        <v>0.93472284040426101</v>
+        <v>1.0125540184924149</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22788,7 +22788,7 @@
         <v>0</v>
       </c>
       <c r="C64">
-        <v>0.24312297718217843</v>
+        <v>0.23397069756846273</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22799,7 +22799,7 @@
         <v>0</v>
       </c>
       <c r="C65">
-        <v>0.45115958475326451</v>
+        <v>0.59788498480590302</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22810,7 +22810,7 @@
         <v>0</v>
       </c>
       <c r="C66">
-        <v>0.37340693775642153</v>
+        <v>0.21923444172631348</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22821,7 +22821,7 @@
         <v>0</v>
       </c>
       <c r="C67">
-        <v>9.9189998679575786E-2</v>
+        <v>-0.14469597281473073</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22832,7 +22832,7 @@
         <v>0</v>
       </c>
       <c r="C68">
-        <v>-0.4665003135094275</v>
+        <v>-0.85275516360636028</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22843,7 +22843,7 @@
         <v>0</v>
       </c>
       <c r="C69">
-        <v>-0.23547344901186018</v>
+        <v>-0.37788923916726802</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22854,7 +22854,7 @@
         <v>0</v>
       </c>
       <c r="C70">
-        <v>-0.72243403579368604</v>
+        <v>-0.64187304473417428</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22865,7 +22865,7 @@
         <v>0</v>
       </c>
       <c r="C71">
-        <v>-0.40660221223658088</v>
+        <v>-0.21062251872389612</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22876,7 +22876,7 @@
         <v>0</v>
       </c>
       <c r="C72">
-        <v>-2.4005713320242362E-2</v>
+        <v>-0.10442563835366861</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22887,7 +22887,7 @@
         <v>0</v>
       </c>
       <c r="C73">
-        <v>5.988848086064763E-2</v>
+        <v>-3.8790698242822164E-2</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22898,7 +22898,7 @@
         <v>0</v>
       </c>
       <c r="C74">
-        <v>5.6242440812075162E-2</v>
+        <v>0.28766571147110837</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22909,7 +22909,7 @@
         <v>0</v>
       </c>
       <c r="C75">
-        <v>7.6143755367983845E-2</v>
+        <v>7.6337886529153368E-2</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22920,7 +22920,7 @@
         <v>0</v>
       </c>
       <c r="C76">
-        <v>-0.21755375577270217</v>
+        <v>0.12922278495220654</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22931,7 +22931,7 @@
         <v>0</v>
       </c>
       <c r="C77">
-        <v>0.16643699432266168</v>
+        <v>0.40357030402439215</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22942,7 +22942,7 @@
         <v>0</v>
       </c>
       <c r="C78">
-        <v>0.11427470414735506</v>
+        <v>0.36974017945270804</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22953,7 +22953,7 @@
         <v>0</v>
       </c>
       <c r="C79">
-        <v>-5.834847980778099E-2</v>
+        <v>0.22210371809174936</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22964,7 +22964,7 @@
         <v>0</v>
       </c>
       <c r="C80">
-        <v>0.20055438349811819</v>
+        <v>0.37613307631205706</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22975,7 +22975,7 @@
         <v>0</v>
       </c>
       <c r="C81">
-        <v>-0.18329308428312158</v>
+        <v>-9.5419982412588408E-2</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22986,7 +22986,7 @@
         <v>0</v>
       </c>
       <c r="C82">
-        <v>-9.7665154304560228E-2</v>
+        <v>0.21218193756888995</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -22997,7 +22997,7 @@
         <v>0</v>
       </c>
       <c r="C83">
-        <v>-0.46712410893411338</v>
+        <v>-0.47418244995091174</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23008,7 +23008,7 @@
         <v>0</v>
       </c>
       <c r="C84">
-        <v>-8.7376452088874748E-2</v>
+        <v>-0.14990183307809252</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23019,7 +23019,7 @@
         <v>0</v>
       </c>
       <c r="C85">
-        <v>0.1288416908858899</v>
+        <v>0.17975647931587294</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23030,7 +23030,7 @@
         <v>0</v>
       </c>
       <c r="C86">
-        <v>0.43340771608611001</v>
+        <v>0.17896182477344927</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23041,7 +23041,7 @@
         <v>0</v>
       </c>
       <c r="C87">
-        <v>-1.3365741490436978</v>
+        <v>-1.0432010512130423</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23052,7 +23052,7 @@
         <v>0</v>
       </c>
       <c r="C88">
-        <v>-0.56638895299888115</v>
+        <v>-0.68787575028408765</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23063,7 +23063,7 @@
         <v>0</v>
       </c>
       <c r="C89">
-        <v>1.1222511844456584</v>
+        <v>0.89768942309768207</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23074,7 +23074,7 @@
         <v>0</v>
       </c>
       <c r="C90">
-        <v>0.57596787166422669</v>
+        <v>0.63934757819038279</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23085,7 +23085,7 @@
         <v>0</v>
       </c>
       <c r="C91">
-        <v>0.68222402245328517</v>
+        <v>0.6260810115381662</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23096,7 +23096,7 @@
         <v>0</v>
       </c>
       <c r="C92">
-        <v>-0.17282740834372493</v>
+        <v>7.1903903847224448E-2</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23107,7 +23107,7 @@
         <v>0</v>
       </c>
       <c r="C93">
-        <v>0.47638087867723872</v>
+        <v>0.64691835566642297</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23118,7 +23118,7 @@
         <v>0</v>
       </c>
       <c r="C94">
-        <v>0.15095354541900419</v>
+        <v>-5.880429966361158E-2</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23129,7 +23129,7 @@
         <v>0</v>
       </c>
       <c r="C95">
-        <v>0.71983207142228478</v>
+        <v>0.81101469674894411</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23140,7 +23140,7 @@
         <v>0</v>
       </c>
       <c r="C96">
-        <v>0.46666592449048261</v>
+        <v>0.5352441135893079</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23151,7 +23151,7 @@
         <v>0</v>
       </c>
       <c r="C97">
-        <v>-9.5789319393920963E-2</v>
+        <v>-0.1302547347662367</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23162,7 +23162,7 @@
         <v>0</v>
       </c>
       <c r="C98">
-        <v>-0.65420699505883106</v>
+        <v>-0.49890276233852843</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23173,7 +23173,7 @@
         <v>0</v>
       </c>
       <c r="C99">
-        <v>-0.53181383129202053</v>
+        <v>-0.23219904429791832</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23184,7 +23184,7 @@
         <v>0</v>
       </c>
       <c r="C100">
-        <v>-0.20461621682345432</v>
+        <v>-0.2429188857942558</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23195,7 +23195,7 @@
         <v>0</v>
       </c>
       <c r="C101">
-        <v>0.21633438117178655</v>
+        <v>0.41347702319024432</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23206,7 +23206,7 @@
         <v>0</v>
       </c>
       <c r="C102">
-        <v>0.25370515970682095</v>
+        <v>0.14623514389907122</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23217,7 +23217,7 @@
         <v>0</v>
       </c>
       <c r="C103">
-        <v>1.6347923414114358E-2</v>
+        <v>-2.8108727825715177E-2</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23228,7 +23228,7 @@
         <v>0.20094261628094226</v>
       </c>
       <c r="C104">
-        <v>0.35325347839295473</v>
+        <v>0.51267735102689516</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23239,7 +23239,7 @@
         <v>0</v>
       </c>
       <c r="C105">
-        <v>-0.22775247213114111</v>
+        <v>-0.11718112101708268</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23250,7 +23250,7 @@
         <v>0</v>
       </c>
       <c r="C106">
-        <v>0.16555386561827032</v>
+        <v>0.37671074756965567</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23261,7 +23261,7 @@
         <v>0</v>
       </c>
       <c r="C107">
-        <v>0.46252130387257334</v>
+        <v>0.48601785517026491</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23272,7 +23272,7 @@
         <v>0</v>
       </c>
       <c r="C108">
-        <v>-1.8729028948628931E-2</v>
+        <v>-2.5761940406411905E-2</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23283,7 +23283,7 @@
         <v>-0.18880190711131353</v>
       </c>
       <c r="C109">
-        <v>-0.29817457268942826</v>
+        <v>-0.18192812811699061</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23294,7 +23294,7 @@
         <v>0</v>
       </c>
       <c r="C110">
-        <v>-0.16217471096096572</v>
+        <v>5.0763842083370932E-2</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23305,7 +23305,7 @@
         <v>0</v>
       </c>
       <c r="C111">
-        <v>-4.3076703757121255E-2</v>
+        <v>-0.10096796752691757</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23316,7 +23316,7 @@
         <v>0</v>
       </c>
       <c r="C112">
-        <v>-0.20246753490475511</v>
+        <v>-3.2946598954649395E-2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23327,7 +23327,7 @@
         <v>0</v>
       </c>
       <c r="C113">
-        <v>0.19589358677523744</v>
+        <v>0.31197549933148638</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23338,7 +23338,7 @@
         <v>0</v>
       </c>
       <c r="C114">
-        <v>-0.27488585709339336</v>
+        <v>-0.37697640860726145</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23349,7 +23349,7 @@
         <v>0</v>
       </c>
       <c r="C115">
-        <v>0.19648399905153119</v>
+        <v>0.25705415975465729</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23360,7 +23360,7 @@
         <v>0.11654615323003828</v>
       </c>
       <c r="C116">
-        <v>6.7293059438816458E-2</v>
+        <v>-3.6387768998430027E-2</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23371,7 +23371,7 @@
         <v>0</v>
       </c>
       <c r="C117">
-        <v>-2.2223893914148023E-2</v>
+        <v>-0.14568630379155786</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23382,7 +23382,7 @@
         <v>0</v>
       </c>
       <c r="C118">
-        <v>7.5553039727362992E-2</v>
+        <v>-1.5664081374299865E-2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23393,7 +23393,7 @@
         <v>1.0414575481015098</v>
       </c>
       <c r="C119">
-        <v>0.11028685361088902</v>
+        <v>0.12829360623678024</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23404,7 +23404,7 @@
         <v>0</v>
       </c>
       <c r="C120">
-        <v>-0.3583025022870262</v>
+        <v>-0.34773294878826833</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23415,7 +23415,7 @@
         <v>-1.3289823080612566</v>
       </c>
       <c r="C121">
-        <v>-0.45881609210593727</v>
+        <v>-0.52264533998888552</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23426,7 +23426,7 @@
         <v>0.52127415129754351</v>
       </c>
       <c r="C122">
-        <v>0.30221358454462188</v>
+        <v>-2.0383241612471632E-2</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23437,7 +23437,7 @@
         <v>0</v>
       </c>
       <c r="C123">
-        <v>0.63876733845106082</v>
+        <v>0.17419801836618218</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23448,7 +23448,7 @@
         <v>0</v>
       </c>
       <c r="C124">
-        <v>0.44127833456619642</v>
+        <v>0.62851734097164946</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23459,7 +23459,7 @@
         <v>0</v>
       </c>
       <c r="C125">
-        <v>8.5354482010195631E-2</v>
+        <v>6.0924288763955621E-2</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23470,7 +23470,7 @@
         <v>0</v>
       </c>
       <c r="C126">
-        <v>-0.51437208098988851</v>
+        <v>-0.36151277398245202</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23481,7 +23481,7 @@
         <v>0</v>
       </c>
       <c r="C127">
-        <v>-8.9635687698043809E-2</v>
+        <v>-9.6944665435421268E-2</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23492,7 +23492,7 @@
         <v>-0.25417794153367984</v>
       </c>
       <c r="C128">
-        <v>0.42154993364897342</v>
+        <v>3.2539931456329221E-3</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23503,7 +23503,7 @@
         <v>0</v>
       </c>
       <c r="C129">
-        <v>-0.14664997240325764</v>
+        <v>-0.11734726487807344</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23514,7 +23514,7 @@
         <v>0</v>
       </c>
       <c r="C130">
-        <v>0.39894792210295105</v>
+        <v>0.20228727420383846</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23525,7 +23525,7 @@
         <v>-1.3786119988987506</v>
       </c>
       <c r="C131">
-        <v>0.79944934519858735</v>
+        <v>0.59678626571069993</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23536,7 +23536,7 @@
         <v>0</v>
       </c>
       <c r="C132">
-        <v>0.73947790739361141</v>
+        <v>0.61870991032709355</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23547,7 +23547,7 @@
         <v>-3.8903888914070412</v>
       </c>
       <c r="C133">
-        <v>-0.53245903834783603</v>
+        <v>-0.47901683291440678</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23558,7 +23558,7 @@
         <v>0</v>
       </c>
       <c r="C134">
-        <v>-0.96162875235502698</v>
+        <v>-0.70471053273154227</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23569,7 +23569,7 @@
         <v>0</v>
       </c>
       <c r="C135">
-        <v>-2.2263351210951772</v>
+        <v>-2.1141531438788772</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23580,7 +23580,7 @@
         <v>0</v>
       </c>
       <c r="C136">
-        <v>-1.070985396824657</v>
+        <v>-0.94794153585236363</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23591,7 +23591,7 @@
         <v>0.51161509403285454</v>
       </c>
       <c r="C137">
-        <v>-0.15326562804958449</v>
+        <v>-0.73291088927173687</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23602,7 +23602,7 @@
         <v>0</v>
       </c>
       <c r="C138">
-        <v>1.1684403091065221</v>
+        <v>1.0702976318834441</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23613,7 +23613,7 @@
         <v>0</v>
       </c>
       <c r="C139">
-        <v>-0.80308205724906168</v>
+        <v>-1.0421451828974451</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23624,7 +23624,7 @@
         <v>0</v>
       </c>
       <c r="C140">
-        <v>-0.86290248220921539</v>
+        <v>-0.72372915684738715</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23635,7 +23635,7 @@
         <v>9.3641710744903168</v>
       </c>
       <c r="C141">
-        <v>2.3683161293234716</v>
+        <v>2.0471469660714061</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23646,7 +23646,7 @@
         <v>0</v>
       </c>
       <c r="C142">
-        <v>-0.9789974905967902</v>
+        <v>-0.75780052501641293</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23657,7 +23657,7 @@
         <v>-1.1085973375193794</v>
       </c>
       <c r="C143">
-        <v>-1.242937687075487E-2</v>
+        <v>-0.18010923583894267</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23668,7 +23668,7 @@
         <v>0</v>
       </c>
       <c r="C144">
-        <v>0.21944443210706932</v>
+        <v>0.26995875760590388</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23679,7 +23679,7 @@
         <v>3.0063113352071746</v>
       </c>
       <c r="C145">
-        <v>0.2901534926854768</v>
+        <v>0.15216262597498234</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23690,7 +23690,7 @@
         <v>0</v>
       </c>
       <c r="C146">
-        <v>1.3799028421315747</v>
+        <v>1.6511628040093469</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23701,7 +23701,7 @@
         <v>0</v>
       </c>
       <c r="C147">
-        <v>-1.0634686944531193</v>
+        <v>-1.0553319096311842</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="C148">
-        <v>0.23696839848770865</v>
+        <v>0.29818075574427266</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23723,7 +23723,7 @@
         <v>0</v>
       </c>
       <c r="C149">
-        <v>0.12529530530800889</v>
+        <v>-1.0267916085213375E-2</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23734,7 +23734,7 @@
         <v>0</v>
       </c>
       <c r="C150">
-        <v>0.22312321121339074</v>
+        <v>0.29959691456951854</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23745,7 +23745,7 @@
         <v>1.2149573871003831</v>
       </c>
       <c r="C151">
-        <v>0.33943287543294742</v>
+        <v>0.49836810947824683</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23756,7 +23756,7 @@
         <v>0</v>
       </c>
       <c r="C152">
-        <v>0.70015302639623811</v>
+        <v>0.59518225229495902</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23767,7 +23767,7 @@
         <v>0</v>
       </c>
       <c r="C153">
-        <v>-0.34429851145056312</v>
+        <v>-3.5011568327522766E-2</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23778,7 +23778,7 @@
         <v>0</v>
       </c>
       <c r="C154">
-        <v>0.30496581881138429</v>
+        <v>0.1679613541293267</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23789,7 +23789,7 @@
         <v>0</v>
       </c>
       <c r="C155">
-        <v>-0.12075157618864552</v>
+        <v>0.14520488503484724</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23800,7 +23800,7 @@
         <v>0</v>
       </c>
       <c r="C156">
-        <v>-0.30297967311944451</v>
+        <v>-0.49042413788388417</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23811,7 +23811,7 @@
         <v>-4.2708107269333144</v>
       </c>
       <c r="C157">
-        <v>-0.86544397494809977</v>
+        <v>-0.52464362429588207</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23822,7 +23822,7 @@
         <v>0</v>
       </c>
       <c r="C158">
-        <v>0.11212735170440623</v>
+        <v>0.57835415126827083</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23833,7 +23833,7 @@
         <v>0</v>
       </c>
       <c r="C159">
-        <v>-0.30884326290759906</v>
+        <v>-0.33338661171784412</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23844,7 +23844,7 @@
         <v>0</v>
       </c>
       <c r="C160">
-        <v>-0.74879727535987362</v>
+        <v>-0.7259782757618306</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23855,7 +23855,7 @@
         <v>0</v>
       </c>
       <c r="C161">
-        <v>0.89957925719853371</v>
+        <v>0.90950413915519313</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23866,7 +23866,7 @@
         <v>0</v>
       </c>
       <c r="C162">
-        <v>-0.55547007203349874</v>
+        <v>-0.48615048050496823</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23877,7 +23877,7 @@
         <v>2.3292152276657569</v>
       </c>
       <c r="C163">
-        <v>-0.83468343452260596</v>
+        <v>-0.74115084591461056</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23888,7 +23888,7 @@
         <v>0</v>
       </c>
       <c r="C164">
-        <v>-0.57607442715392343</v>
+        <v>-0.48822554303515542</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23899,7 +23899,7 @@
         <v>0</v>
       </c>
       <c r="C165">
-        <v>0.43287761965392541</v>
+        <v>0.10707757805601748</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23910,7 +23910,7 @@
         <v>0</v>
       </c>
       <c r="C166">
-        <v>-0.39720163734061448</v>
+        <v>-0.4364003293386956</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23921,7 +23921,7 @@
         <v>0</v>
       </c>
       <c r="C167">
-        <v>-0.23178585276021391</v>
+        <v>-0.33589129683029745</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23932,7 +23932,7 @@
         <v>5.9295095683908778</v>
       </c>
       <c r="C168">
-        <v>-0.20432193509189933</v>
+        <v>-0.32045061051346874</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23943,7 +23943,7 @@
         <v>0</v>
       </c>
       <c r="C169">
-        <v>1.0361085258933835</v>
+        <v>0.86997176267015131</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23954,7 +23954,7 @@
         <v>0</v>
       </c>
       <c r="C170">
-        <v>-7.0053997444024615E-2</v>
+        <v>-4.5856623625505494E-2</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23965,7 +23965,7 @@
         <v>0</v>
       </c>
       <c r="C171">
-        <v>-0.3489685896083482</v>
+        <v>-0.39057667588198952</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23976,7 +23976,7 @@
         <v>0</v>
       </c>
       <c r="C172">
-        <v>0.48448404474068701</v>
+        <v>0.30687598938084248</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23987,7 +23987,7 @@
         <v>0</v>
       </c>
       <c r="C173">
-        <v>0.89161091042384688</v>
+        <v>0.82335201809765235</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -23998,7 +23998,7 @@
         <v>0</v>
       </c>
       <c r="C174">
-        <v>-0.13805169237421572</v>
+        <v>-0.20668995015725422</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24009,7 +24009,7 @@
         <v>-3.1588205500244313</v>
       </c>
       <c r="C175">
-        <v>-7.3453100660753931E-2</v>
+        <v>-0.35330922094564665</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24020,7 +24020,7 @@
         <v>0</v>
       </c>
       <c r="C176">
-        <v>0.48100416241862193</v>
+        <v>0.62235686153877567</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24031,7 +24031,7 @@
         <v>0</v>
       </c>
       <c r="C177">
-        <v>-0.69473934101556412</v>
+        <v>-0.8664081512338816</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24042,7 +24042,7 @@
         <v>0.95204580952703277</v>
       </c>
       <c r="C178">
-        <v>1.0547627926664429</v>
+        <v>0.86058178599028334</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24053,7 +24053,7 @@
         <v>0</v>
       </c>
       <c r="C179">
-        <v>0.47167363317076844</v>
+        <v>0.34512785304511356</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24064,7 +24064,7 @@
         <v>-1.821002143823117</v>
       </c>
       <c r="C180">
-        <v>0.10987759479729373</v>
+        <v>5.4755240556449744E-2</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24075,7 +24075,7 @@
         <v>0</v>
       </c>
       <c r="C181">
-        <v>0.43573311307271573</v>
+        <v>0.42223311368192706</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24086,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="C182">
-        <v>0.87709957264913674</v>
+        <v>0.86433947689880541</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24097,7 +24097,7 @@
         <v>0</v>
       </c>
       <c r="C183">
-        <v>-0.92399187276574113</v>
+        <v>-0.81499311075371783</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24108,7 +24108,7 @@
         <v>0</v>
       </c>
       <c r="C184">
-        <v>-0.23111190798218309</v>
+        <v>-0.13691377606032246</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24119,7 +24119,7 @@
         <v>0</v>
       </c>
       <c r="C185">
-        <v>-0.45644293794079127</v>
+        <v>-2.8735515550997445E-2</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24130,7 +24130,7 @@
         <v>0</v>
       </c>
       <c r="C186">
-        <v>-0.63236457089587372</v>
+        <v>-0.76907392432782107</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24141,7 +24141,7 @@
         <v>0</v>
       </c>
       <c r="C187">
-        <v>-2.3274304973313474E-2</v>
+        <v>7.4732652932079757E-2</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24152,7 +24152,7 @@
         <v>0.45974167493349005</v>
       </c>
       <c r="C188">
-        <v>0.86879012578985493</v>
+        <v>0.55881820531536974</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24163,7 +24163,7 @@
         <v>0</v>
       </c>
       <c r="C189">
-        <v>1.5089854018625914</v>
+        <v>1.5830017114823967</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24174,7 +24174,7 @@
         <v>0</v>
       </c>
       <c r="C190">
-        <v>0.94088114895194908</v>
+        <v>0.70193611551826463</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24185,7 +24185,7 @@
         <v>0</v>
       </c>
       <c r="C191">
-        <v>0.24818018790765908</v>
+        <v>0.31573189103256422</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24196,7 +24196,7 @@
         <v>0</v>
       </c>
       <c r="C192">
-        <v>-0.53432507749098335</v>
+        <v>-0.77227187252416496</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24207,7 +24207,7 @@
         <v>2.7755270583246179</v>
       </c>
       <c r="C193">
-        <v>-2.1152804248410694E-4</v>
+        <v>-0.2803490157845171</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24218,7 +24218,7 @@
         <v>0</v>
       </c>
       <c r="C194">
-        <v>1.8634700445268375E-2</v>
+        <v>-0.15765055936533373</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24229,7 +24229,7 @@
         <v>0</v>
       </c>
       <c r="C195">
-        <v>-0.92430624179254461</v>
+        <v>-1.1249882005419258</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24240,7 +24240,7 @@
         <v>3.1147766504221419</v>
       </c>
       <c r="C196">
-        <v>0.44703217638272169</v>
+        <v>0.48690163660136737</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24251,7 +24251,7 @@
         <v>0</v>
       </c>
       <c r="C197">
-        <v>4.8088239787840201E-2</v>
+        <v>-0.20007685393445102</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24262,7 +24262,7 @@
         <v>0</v>
       </c>
       <c r="C198">
-        <v>-0.33136983522279295</v>
+        <v>-0.49090189919318217</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24273,7 +24273,7 @@
         <v>-0.60165622475868197</v>
       </c>
       <c r="C199">
-        <v>-0.34895271934609612</v>
+        <v>-0.45309861900218196</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24284,7 +24284,7 @@
         <v>0</v>
       </c>
       <c r="C200">
-        <v>0.20927747142907999</v>
+        <v>3.1174274429341321E-2</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24295,7 +24295,7 @@
         <v>0</v>
       </c>
       <c r="C201">
-        <v>-0.21784124688324252</v>
+        <v>-0.12992176507794995</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24306,7 +24306,7 @@
         <v>8.5974608677910944E-2</v>
       </c>
       <c r="C202">
-        <v>0.15190043288915625</v>
+        <v>0.28889605242135125</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24317,7 +24317,7 @@
         <v>0</v>
       </c>
       <c r="C203">
-        <v>0.6429205074848281</v>
+        <v>0.53486667383798703</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24328,7 +24328,7 @@
         <v>1.6266264401273489</v>
       </c>
       <c r="C204">
-        <v>4.847951674500665E-4</v>
+        <v>6.2463437228568779E-2</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24339,7 +24339,7 @@
         <v>0</v>
       </c>
       <c r="C205">
-        <v>-0.55303295630299532</v>
+        <v>-0.55000108641290957</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24350,7 +24350,7 @@
         <v>0</v>
       </c>
       <c r="C206">
-        <v>0.10777155320408281</v>
+        <v>-6.1637427700740398E-2</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24361,7 +24361,7 @@
         <v>-5.5462214920600301</v>
       </c>
       <c r="C207">
-        <v>0.12170836499060347</v>
+        <v>0.11632628257897802</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24372,7 +24372,7 @@
         <v>0</v>
       </c>
       <c r="C208">
-        <v>-0.32638746554331438</v>
+        <v>-0.26128416992023018</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24383,7 +24383,7 @@
         <v>0</v>
       </c>
       <c r="C209">
-        <v>0.29901592079964179</v>
+        <v>0.3514136458631188</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24394,7 +24394,7 @@
         <v>4.1044346257687279</v>
       </c>
       <c r="C210">
-        <v>-5.4913071959616352E-2</v>
+        <v>0.39711152727576665</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24405,7 +24405,7 @@
         <v>0</v>
       </c>
       <c r="C211">
-        <v>0.54086613232681213</v>
+        <v>0.44424548950761816</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24416,7 +24416,7 @@
         <v>0</v>
       </c>
       <c r="C212">
-        <v>-0.7809435532484732</v>
+        <v>-0.73197302355148552</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24427,7 +24427,7 @@
         <v>0</v>
       </c>
       <c r="C213">
-        <v>0.54456321125402807</v>
+        <v>0.66526512579128683</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24438,7 +24438,7 @@
         <v>-0.60517666792897118</v>
       </c>
       <c r="C214">
-        <v>0.11844683653831294</v>
+        <v>0.11823961791990234</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24449,7 +24449,7 @@
         <v>0</v>
       </c>
       <c r="C215">
-        <v>-9.1554377522740843E-2</v>
+        <v>-1.1908256434374404E-2</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24460,7 +24460,7 @@
         <v>-1.4945262392643579</v>
       </c>
       <c r="C216">
-        <v>-0.1242656164989597</v>
+        <v>0.1240989352251288</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24471,7 +24471,7 @@
         <v>0</v>
       </c>
       <c r="C217">
-        <v>-3.9067696254731082E-2</v>
+        <v>0.33055308090215962</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24482,7 +24482,7 @@
         <v>0</v>
       </c>
       <c r="C218">
-        <v>0.14026652977835588</v>
+        <v>0.14802294782474723</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24493,7 +24493,7 @@
         <v>-0.15661004410084348</v>
       </c>
       <c r="C219">
-        <v>0.24479534058524216</v>
+        <v>7.8757119551159618E-2</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24504,7 +24504,7 @@
         <v>0</v>
       </c>
       <c r="C220">
-        <v>-7.4163644193675743E-2</v>
+        <v>-0.15332422608050444</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24515,7 +24515,7 @@
         <v>0</v>
       </c>
       <c r="C221">
-        <v>-9.1411405749299499E-2</v>
+        <v>7.121655620532015E-2</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24526,7 +24526,7 @@
         <v>0</v>
       </c>
       <c r="C222">
-        <v>1.1226313229078457E-3</v>
+        <v>0.22157201137927676</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24537,7 +24537,7 @@
         <v>-1.3152768715984233</v>
       </c>
       <c r="C223">
-        <v>-0.66637217957169714</v>
+        <v>-0.55993470520522648</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24548,7 +24548,7 @@
         <v>0</v>
       </c>
       <c r="C224">
-        <v>-0.12376625584264268</v>
+        <v>-0.16076110430309568</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24559,7 +24559,7 @@
         <v>0</v>
       </c>
       <c r="C225">
-        <v>0.1905361110850422</v>
+        <v>0.17398664222173893</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24570,7 +24570,7 @@
         <v>0.23773326668811351</v>
       </c>
       <c r="C226">
-        <v>-0.41216906649697183</v>
+        <v>-0.43787347139513866</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24581,7 +24581,7 @@
         <v>0</v>
       </c>
       <c r="C227">
-        <v>0.48082431263838055</v>
+        <v>0.4458608840560716</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24592,7 +24592,7 @@
         <v>-5.267852793433339</v>
       </c>
       <c r="C228">
-        <v>-0.75506088421639661</v>
+        <v>-0.59898876878324891</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24603,7 +24603,7 @@
         <v>0</v>
       </c>
       <c r="C229">
-        <v>-0.81623418487768606</v>
+        <v>-0.62807035612902995</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24614,7 +24614,7 @@
         <v>0</v>
       </c>
       <c r="C230">
-        <v>0.3827579799956482</v>
+        <v>0.47810046230008107</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24625,7 +24625,7 @@
         <v>0</v>
       </c>
       <c r="C231">
-        <v>-0.22221200817712214</v>
+        <v>-0.37845379296164094</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24636,7 +24636,7 @@
         <v>-4.9586560199161314</v>
       </c>
       <c r="C232">
-        <v>-0.58764454954699574</v>
+        <v>-0.50882943432318128</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24647,7 +24647,7 @@
         <v>0</v>
       </c>
       <c r="C233">
-        <v>0.57877336912698896</v>
+        <v>0.37786892522692267</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24658,7 +24658,7 @@
         <v>0</v>
       </c>
       <c r="C234">
-        <v>0.15175258960042232</v>
+        <v>0.22983901534262782</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24669,7 +24669,7 @@
         <v>-0.62220043165402683</v>
       </c>
       <c r="C235">
-        <v>8.5354092116042765E-2</v>
+        <v>-3.7744994252084288E-2</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24680,7 +24680,7 @@
         <v>0</v>
       </c>
       <c r="C236">
-        <v>0.26851077610217267</v>
+        <v>0.46534058716849724</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24691,7 +24691,7 @@
         <v>0</v>
       </c>
       <c r="C237">
-        <v>-0.41650209205818084</v>
+        <v>-0.6520674737255634</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24702,7 +24702,7 @@
         <v>0</v>
       </c>
       <c r="C238">
-        <v>-0.14525439526362632</v>
+        <v>-0.16942852893407812</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24713,7 +24713,7 @@
         <v>0</v>
       </c>
       <c r="C239">
-        <v>-0.11323874932994263</v>
+        <v>-0.1172347442316178</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24724,7 +24724,7 @@
         <v>1.7201532821127614</v>
       </c>
       <c r="C240">
-        <v>0.11945319754803368</v>
+        <v>-2.1668111296842842E-2</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24735,7 +24735,7 @@
         <v>0</v>
       </c>
       <c r="C241">
-        <v>-0.56618977499955492</v>
+        <v>-0.50543767873293466</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24746,7 +24746,7 @@
         <v>0</v>
       </c>
       <c r="C242">
-        <v>0.4223821375444794</v>
+        <v>0.32222317306956605</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24757,7 +24757,7 @@
         <v>0</v>
       </c>
       <c r="C243">
-        <v>0.25132174622995951</v>
+        <v>0.2581398831214029</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24768,7 +24768,7 @@
         <v>0</v>
       </c>
       <c r="C244">
-        <v>-0.44017104156122316</v>
+        <v>-0.47533395653034605</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24779,7 +24779,7 @@
         <v>0</v>
       </c>
       <c r="C245">
-        <v>0.72913725897327841</v>
+        <v>0.63017903617316728</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24790,7 +24790,7 @@
         <v>0</v>
       </c>
       <c r="C246">
-        <v>-0.41076205054631781</v>
+        <v>-0.57746178850534968</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24801,7 +24801,7 @@
         <v>0.38945682625939493</v>
       </c>
       <c r="C247">
-        <v>-0.61454697277634762</v>
+        <v>-0.29523854416074446</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24812,7 +24812,7 @@
         <v>0</v>
       </c>
       <c r="C248">
-        <v>0.13071565585638831</v>
+        <v>7.301677199437423E-2</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24823,7 +24823,7 @@
         <v>0</v>
       </c>
       <c r="C249">
-        <v>-0.17339130275148673</v>
+        <v>-0.22524158679404524</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24834,7 +24834,7 @@
         <v>0</v>
       </c>
       <c r="C250">
-        <v>0.29743146136637455</v>
+        <v>0.30624438110053653</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24845,7 +24845,7 @@
         <v>0</v>
       </c>
       <c r="C251">
-        <v>-0.26618156309976487</v>
+        <v>-0.15850856195062951</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24856,7 +24856,7 @@
         <v>-9.486315291733903E-2</v>
       </c>
       <c r="C252">
-        <v>-3.7281582754022345E-2</v>
+        <v>-7.1149659286998873E-2</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24867,7 +24867,7 @@
         <v>0</v>
       </c>
       <c r="C253">
-        <v>0.28280424034971596</v>
+        <v>0.21049160938934747</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24878,7 +24878,7 @@
         <v>0</v>
       </c>
       <c r="C254">
-        <v>0.3056367453153811</v>
+        <v>7.2294228560250223E-2</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24889,7 +24889,7 @@
         <v>0</v>
       </c>
       <c r="C255">
-        <v>-0.60480710968864027</v>
+        <v>-0.35289330902544153</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24900,7 +24900,7 @@
         <v>0</v>
       </c>
       <c r="C256">
-        <v>1.1084883256522076</v>
+        <v>1.100395032519619</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24911,7 +24911,7 @@
         <v>0</v>
       </c>
       <c r="C257">
-        <v>0.15661726315136767</v>
+        <v>0.33365436457190756</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24922,7 +24922,7 @@
         <v>0</v>
       </c>
       <c r="C258">
-        <v>-1.1473039785276868</v>
+        <v>-1.2003061712875924</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24933,7 +24933,7 @@
         <v>0.98548755853846426</v>
       </c>
       <c r="C259">
-        <v>0.19031160801481578</v>
+        <v>0.35281032706000215</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24944,7 +24944,7 @@
         <v>0</v>
       </c>
       <c r="C260">
-        <v>0.39369870221539977</v>
+        <v>0.20938323463552491</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24955,7 +24955,7 @@
         <v>0</v>
       </c>
       <c r="C261">
-        <v>-0.2356810168091886</v>
+        <v>1.5049603658869704E-2</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24966,7 +24966,7 @@
         <v>0</v>
       </c>
       <c r="C262">
-        <v>0.56269139911166455</v>
+        <v>0.50399684713728943</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24977,7 +24977,7 @@
         <v>0</v>
       </c>
       <c r="C263">
-        <v>0.19319620472398033</v>
+        <v>0.20783456487848401</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24988,7 +24988,7 @@
         <v>4.0227311693148113</v>
       </c>
       <c r="C264">
-        <v>-0.58901648455888356</v>
+        <v>-0.58740785993446243</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -24999,7 +24999,7 @@
         <v>0</v>
       </c>
       <c r="C265">
-        <v>0.6609978182423657</v>
+        <v>0.54153339490553731</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25010,7 +25010,7 @@
         <v>0</v>
       </c>
       <c r="C266">
-        <v>-0.21545284877132478</v>
+        <v>-0.19435548463671051</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25021,7 +25021,7 @@
         <v>0</v>
       </c>
       <c r="C267">
-        <v>-1.1073051161553262</v>
+        <v>-1.1746107439254956</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25032,7 +25032,7 @@
         <v>0</v>
       </c>
       <c r="C268">
-        <v>-0.22591678903425366</v>
+        <v>-7.8606895172134067E-2</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25043,7 +25043,7 @@
         <v>0</v>
       </c>
       <c r="C269">
-        <v>-0.25693521528291996</v>
+        <v>-0.52438773878777145</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25054,7 +25054,7 @@
         <v>0</v>
       </c>
       <c r="C270">
-        <v>-3.7447132975779958E-2</v>
+        <v>1.7922952551572897E-2</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25065,7 +25065,7 @@
         <v>-2.1318792040593819</v>
       </c>
       <c r="C271">
-        <v>-1.0316299574005867</v>
+        <v>-1.1567450999790352</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25076,7 +25076,7 @@
         <v>0</v>
       </c>
       <c r="C272">
-        <v>-0.20789705327921976</v>
+        <v>-0.2769364022700021</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25087,7 +25087,7 @@
         <v>0</v>
       </c>
       <c r="C273">
-        <v>-0.11970964228171696</v>
+        <v>-0.21309884774826329</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25098,7 +25098,7 @@
         <v>0</v>
       </c>
       <c r="C274">
-        <v>-0.29870127743616831</v>
+        <v>-0.18744127236802169</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25109,7 +25109,7 @@
         <v>0</v>
       </c>
       <c r="C275">
-        <v>0.2348710051453079</v>
+        <v>7.0138995705484125E-2</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25120,7 +25120,7 @@
         <v>0</v>
       </c>
       <c r="C276">
-        <v>-0.61090427022062443</v>
+        <v>-0.12551342964589762</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25131,7 +25131,7 @@
         <v>-0.7243565712090988</v>
       </c>
       <c r="C277">
-        <v>-0.61380290217911149</v>
+        <v>-0.34474649444211269</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25142,7 +25142,7 @@
         <v>0</v>
       </c>
       <c r="C278">
-        <v>-0.4595101595722631</v>
+        <v>-0.39893681826908423</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25153,7 +25153,7 @@
         <v>0</v>
       </c>
       <c r="C279">
-        <v>-0.12731949904276157</v>
+        <v>9.7810852002900486E-3</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25164,7 +25164,7 @@
         <v>-2.4001352563022373</v>
       </c>
       <c r="C280">
-        <v>-0.62255058960283571</v>
+        <v>-0.73223802211059486</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25175,7 +25175,7 @@
         <v>0</v>
       </c>
       <c r="C281">
-        <v>-9.2326517809602798E-2</v>
+        <v>0.17188118932127644</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25186,7 +25186,7 @@
         <v>0</v>
       </c>
       <c r="C282">
-        <v>-0.60978748336336031</v>
+        <v>-0.19754962606025642</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25197,7 +25197,7 @@
         <v>-0.31879532673724803</v>
       </c>
       <c r="C283">
-        <v>-0.32600511905333246</v>
+        <v>-0.27292596537149788</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25208,7 +25208,7 @@
         <v>0</v>
       </c>
       <c r="C284">
-        <v>0.2259038265192265</v>
+        <v>0.16772418812241624</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25219,7 +25219,7 @@
         <v>0</v>
       </c>
       <c r="C285">
-        <v>-1.4737799686656918</v>
+        <v>-1.0127973411958293</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25230,7 +25230,7 @@
         <v>0</v>
       </c>
       <c r="C286">
-        <v>0.73482828170515779</v>
+        <v>0.66022755789342824</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25241,7 +25241,7 @@
         <v>0</v>
       </c>
       <c r="C287">
-        <v>-0.92684446123879993</v>
+        <v>-0.49170737089723571</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25252,7 +25252,7 @@
         <v>-2.6942767934376715</v>
       </c>
       <c r="C288">
-        <v>-0.58743314117615142</v>
+        <v>-0.49317115425412872</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25263,7 +25263,7 @@
         <v>0</v>
       </c>
       <c r="C289">
-        <v>-0.87818193949573775</v>
+        <v>-0.72387943824587331</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25274,7 +25274,7 @@
         <v>0</v>
       </c>
       <c r="C290">
-        <v>0.83742901720141893</v>
+        <v>0.91884437922077677</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25285,7 +25285,7 @@
         <v>0</v>
       </c>
       <c r="C291">
-        <v>-0.97440971490894213</v>
+        <v>-0.766499461057214</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25296,7 +25296,7 @@
         <v>-1.7162090431301049</v>
       </c>
       <c r="C292">
-        <v>0.85255409761447143</v>
+        <v>0.79588755658099242</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25307,7 +25307,7 @@
         <v>0</v>
       </c>
       <c r="C293">
-        <v>0.54791965283337374</v>
+        <v>0.69300998165738825</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25318,7 +25318,7 @@
         <v>0</v>
       </c>
       <c r="C294">
-        <v>-0.50773861372570672</v>
+        <v>-0.32673855940408364</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25329,7 +25329,7 @@
         <v>0</v>
       </c>
       <c r="C295">
-        <v>-0.33448602617530254</v>
+        <v>-0.37747602247155965</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25340,7 +25340,7 @@
         <v>0</v>
       </c>
       <c r="C296">
-        <v>0.90648916860385009</v>
+        <v>1.0262755382077762</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25351,7 +25351,7 @@
         <v>0</v>
       </c>
       <c r="C297">
-        <v>3.1065682445840497E-3</v>
+        <v>-6.0089721942724175E-2</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25362,7 +25362,7 @@
         <v>-1.2037790806092841</v>
       </c>
       <c r="C298">
-        <v>1.1412820410224971</v>
+        <v>1.0725975293466847</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25373,7 +25373,7 @@
         <v>0</v>
       </c>
       <c r="C299">
-        <v>-1.1308457394924973</v>
+        <v>-1.0813700522541563</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25384,7 +25384,7 @@
         <v>0</v>
       </c>
       <c r="C300">
-        <v>0.7467428767456501</v>
+        <v>0.62168268432315688</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25395,7 +25395,7 @@
         <v>0</v>
       </c>
       <c r="C301">
-        <v>-0.16542168769101509</v>
+        <v>-0.18669250624461267</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25406,7 +25406,7 @@
         <v>0</v>
       </c>
       <c r="C302">
-        <v>0.57973318562174947</v>
+        <v>0.57203198885252571</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25417,7 +25417,7 @@
         <v>0</v>
       </c>
       <c r="C303">
-        <v>0.39288284685634062</v>
+        <v>0.16462971554179101</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25428,7 +25428,7 @@
         <v>0.74028628090042581</v>
       </c>
       <c r="C304">
-        <v>0.20608894941321398</v>
+        <v>0.18723768806232038</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25439,7 +25439,7 @@
         <v>0</v>
       </c>
       <c r="C305">
-        <v>-1.3323142049573649</v>
+        <v>-1.568341170298865</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25450,7 +25450,7 @@
         <v>0</v>
       </c>
       <c r="C306">
-        <v>0.99830771497743398</v>
+        <v>0.83277634939033485</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25461,7 +25461,7 @@
         <v>-0.69277641604209494</v>
       </c>
       <c r="C307">
-        <v>0.61724641441250483</v>
+        <v>0.52558051601194744</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25472,7 +25472,7 @@
         <v>0</v>
       </c>
       <c r="C308">
-        <v>-0.44423100671028998</v>
+        <v>-0.41243300144163114</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25483,7 +25483,7 @@
         <v>0</v>
       </c>
       <c r="C309">
-        <v>0.56335147820783216</v>
+        <v>0.15126265071974263</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25494,7 +25494,7 @@
         <v>3.9388345631040704</v>
       </c>
       <c r="C310">
-        <v>0.72432633684179315</v>
+        <v>0.78328906359456629</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25505,7 +25505,7 @@
         <v>0</v>
       </c>
       <c r="C311">
-        <v>-0.15662013536450042</v>
+        <v>-0.47388916459207509</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25516,7 +25516,7 @@
         <v>0.66268066524758673</v>
       </c>
       <c r="C312">
-        <v>0.24250739311985681</v>
+        <v>0.131407829965241</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25527,7 +25527,7 @@
         <v>0</v>
       </c>
       <c r="C313">
-        <v>-1.2738604796784447</v>
+        <v>-1.1547877445935013</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25538,7 +25538,7 @@
         <v>-1.2654289453625536</v>
       </c>
       <c r="C314">
-        <v>0.96659799854794903</v>
+        <v>0.91215790199332825</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25549,7 +25549,7 @@
         <v>0</v>
       </c>
       <c r="C315">
-        <v>-8.4688091638251028E-2</v>
+        <v>-0.23496841446135236</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25560,7 +25560,7 @@
         <v>-0.43707052420210213</v>
       </c>
       <c r="C316">
-        <v>-0.54967370318985931</v>
+        <v>-0.28232111592355175</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25571,7 +25571,7 @@
         <v>0</v>
       </c>
       <c r="C317">
-        <v>-0.10650504566762661</v>
+        <v>-0.13350104994165551</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25582,7 +25582,7 @@
         <v>0</v>
       </c>
       <c r="C318">
-        <v>0.31089148011089396</v>
+        <v>0.382852075927612</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25593,7 +25593,7 @@
         <v>0.99114878595594691</v>
       </c>
       <c r="C319">
-        <v>-0.26217889069790351</v>
+        <v>-0.13117614844802208</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25604,7 +25604,7 @@
         <v>2.059923297420696</v>
       </c>
       <c r="C320">
-        <v>-0.15896895909219658</v>
+        <v>-0.23823527068152017</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25615,7 +25615,7 @@
         <v>0</v>
       </c>
       <c r="C321">
-        <v>3.4751617299831741E-2</v>
+        <v>-8.2624191245046955E-2</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25626,7 +25626,7 @@
         <v>1.7802506509155089</v>
       </c>
       <c r="C322">
-        <v>-0.2115741230330673</v>
+        <v>8.4466551067267095E-2</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25637,7 +25637,7 @@
         <v>0</v>
       </c>
       <c r="C323">
-        <v>-1.0018689600537247</v>
+        <v>-0.89342005449513373</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25648,7 +25648,7 @@
         <v>-7.1532748348588759</v>
       </c>
       <c r="C324">
-        <v>-0.5307759190672644</v>
+        <v>-0.33380428820602753</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25659,7 +25659,7 @@
         <v>-1.8641529594572219</v>
       </c>
       <c r="C325">
-        <v>-1.7219626686902099E-2</v>
+        <v>0.11088930918140441</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25670,7 +25670,7 @@
         <v>0</v>
       </c>
       <c r="C326">
-        <v>-0.43495292579310174</v>
+        <v>-0.43652717969587573</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25681,7 +25681,7 @@
         <v>0</v>
       </c>
       <c r="C327">
-        <v>0.52923114617128031</v>
+        <v>0.5805748370697893</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25692,7 +25692,7 @@
         <v>6.0959232725170426E-2</v>
       </c>
       <c r="C328">
-        <v>0.42678572123542019</v>
+        <v>0.47071460575224844</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25703,7 +25703,7 @@
         <v>0</v>
       </c>
       <c r="C329">
-        <v>-1.1075302755690757E-2</v>
+        <v>0.20330681040741025</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25714,7 +25714,7 @@
         <v>0</v>
       </c>
       <c r="C330">
-        <v>-0.12332319981864069</v>
+        <v>-0.14838047495415302</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25725,7 +25725,7 @@
         <v>1.1455581232954777</v>
       </c>
       <c r="C331">
-        <v>-0.8582987895001567</v>
+        <v>-0.4702354485716006</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25736,7 +25736,7 @@
         <v>0</v>
       </c>
       <c r="C332">
-        <v>0.45476524612713265</v>
+        <v>0.26085053817494863</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25747,7 +25747,7 @@
         <v>0</v>
       </c>
       <c r="C333">
-        <v>0.37548080563975789</v>
+        <v>0.4341383730394186</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25758,7 +25758,7 @@
         <v>0.81558688689672831</v>
       </c>
       <c r="C334">
-        <v>0.24229960763542527</v>
+        <v>0.15397994398388445</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25769,7 +25769,7 @@
         <v>0</v>
       </c>
       <c r="C335">
-        <v>2.1244839708836394E-2</v>
+        <v>3.3168315587465066E-2</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25780,7 +25780,7 @@
         <v>0</v>
       </c>
       <c r="C336">
-        <v>-0.73951610491768693</v>
+        <v>-0.56422383491186812</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25791,7 +25791,7 @@
         <v>1.6933051824510181</v>
       </c>
       <c r="C337">
-        <v>0.98900421456425169</v>
+        <v>1.3083590946087611</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25802,7 +25802,7 @@
         <v>2.0142953371343619</v>
       </c>
       <c r="C338">
-        <v>0.64616636957802887</v>
+        <v>0.44788792665105626</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25813,7 +25813,7 @@
         <v>0</v>
       </c>
       <c r="C339">
-        <v>0.71059757836274751</v>
+        <v>0.48096775905832195</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25824,7 +25824,7 @@
         <v>3.8106800365223536E-3</v>
       </c>
       <c r="C340">
-        <v>-0.44564822768583584</v>
+        <v>-0.47334717723633501</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25835,7 +25835,7 @@
         <v>0.78965419774032464</v>
       </c>
       <c r="C341">
-        <v>-1.3785409497368071</v>
+        <v>-1.4206962739242897</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25846,7 +25846,7 @@
         <v>0</v>
       </c>
       <c r="C342">
-        <v>5.2248492358376655E-2</v>
+        <v>0.27051603514780009</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25857,7 +25857,7 @@
         <v>0.91851004192364971</v>
       </c>
       <c r="C343">
-        <v>0.33323053575833594</v>
+        <v>0.35264574550989436</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25868,7 +25868,7 @@
         <v>2.3820825710163723E-2</v>
       </c>
       <c r="C344">
-        <v>-6.4904465537807307E-2</v>
+        <v>-0.16409450977639231</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25879,7 +25879,7 @@
         <v>0</v>
       </c>
       <c r="C345">
-        <v>0.58085929665983582</v>
+        <v>0.34495928174885565</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25890,7 +25890,7 @@
         <v>2.467809819394001</v>
       </c>
       <c r="C346">
-        <v>-1.013176017054306</v>
+        <v>-0.64652080624329089</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25901,7 +25901,7 @@
         <v>0</v>
       </c>
       <c r="C347">
-        <v>0.73410903735380462</v>
+        <v>0.1750626412310394</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25912,7 +25912,7 @@
         <v>0</v>
       </c>
       <c r="C348">
-        <v>-0.43676049946236406</v>
+        <v>-2.7771431893150664E-2</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25923,7 +25923,7 @@
         <v>0.89337155639377197</v>
       </c>
       <c r="C349">
-        <v>0.32573189975186678</v>
+        <v>-0.17462251701923556</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25934,7 +25934,7 @@
         <v>0</v>
       </c>
       <c r="C350">
-        <v>0.33651082392023801</v>
+        <v>0.4325555502913736</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25945,7 +25945,7 @@
         <v>2.6707868568722848</v>
       </c>
       <c r="C351">
-        <v>7.4866045789227065E-2</v>
+        <v>-3.5466389293284752E-2</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25956,7 +25956,7 @@
         <v>-0.68763323602767645</v>
       </c>
       <c r="C352">
-        <v>0.48124582598130289</v>
+        <v>0.40979166695232327</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25967,7 +25967,7 @@
         <v>0</v>
       </c>
       <c r="C353">
-        <v>-0.47359557614299153</v>
+        <v>-0.48884166131994361</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25978,7 +25978,7 @@
         <v>0</v>
       </c>
       <c r="C354">
-        <v>0.46747362166643142</v>
+        <v>0.51451173086666557</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -25989,7 +25989,7 @@
         <v>-0.88918292813691646</v>
       </c>
       <c r="C355">
-        <v>0.11408324987254738</v>
+        <v>-4.8502944315817323E-2</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26000,7 +26000,7 @@
         <v>0</v>
       </c>
       <c r="C356">
-        <v>7.4060552536320365E-2</v>
+        <v>-0.21441683656370383</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26011,7 +26011,7 @@
         <v>0</v>
       </c>
       <c r="C357">
-        <v>0.44107396135567384</v>
+        <v>0.65032182560972118</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26022,7 +26022,7 @@
         <v>-1.6259691262760134</v>
       </c>
       <c r="C358">
-        <v>0.2520299340448211</v>
+        <v>-8.1587160180676119E-2</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26033,7 +26033,7 @@
         <v>0</v>
       </c>
       <c r="C359">
-        <v>0.83275451519109955</v>
+        <v>0.97130618753237774</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26044,7 +26044,7 @@
         <v>0</v>
       </c>
       <c r="C360">
-        <v>-0.49989696727165595</v>
+        <v>-0.322812636594633</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26055,7 +26055,7 @@
         <v>-3.1768297755971129</v>
       </c>
       <c r="C361">
-        <v>-1.0156972341769015</v>
+        <v>-1.0283546817307587</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26066,7 +26066,7 @@
         <v>2.1372721360176112</v>
       </c>
       <c r="C362">
-        <v>0.48510704007862471</v>
+        <v>0.41390771354063915</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26077,7 +26077,7 @@
         <v>0</v>
       </c>
       <c r="C363">
-        <v>4.8995302148020017E-2</v>
+        <v>0.11118237012626961</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26088,7 +26088,7 @@
         <v>3.0186128573050195</v>
       </c>
       <c r="C364">
-        <v>0.84414037503585726</v>
+        <v>0.68259547953422528</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26099,7 +26099,7 @@
         <v>0</v>
       </c>
       <c r="C365">
-        <v>-0.54281411203558383</v>
+        <v>-0.50964347920915731</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26110,7 +26110,7 @@
         <v>0</v>
       </c>
       <c r="C366">
-        <v>-0.45585937052038411</v>
+        <v>-0.27377553239656566</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26121,7 +26121,7 @@
         <v>0.31663005434231678</v>
       </c>
       <c r="C367">
-        <v>0.84329633977102025</v>
+        <v>0.5739028516091087</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26132,7 +26132,7 @@
         <v>0</v>
       </c>
       <c r="C368">
-        <v>0.42467946292821496</v>
+        <v>0.62646203792768307</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26143,7 +26143,7 @@
         <v>0</v>
       </c>
       <c r="C369">
-        <v>0.87615628076997099</v>
+        <v>0.80192746972679407</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26154,7 +26154,7 @@
         <v>-1.6830543051646885</v>
       </c>
       <c r="C370">
-        <v>1.2886181202556171</v>
+        <v>1.2017764859842186</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26165,7 +26165,7 @@
         <v>0</v>
       </c>
       <c r="C371">
-        <v>-1.1459097989017459</v>
+        <v>-1.1656532763083467</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26176,7 +26176,7 @@
         <v>0</v>
       </c>
       <c r="C372">
-        <v>-1.1430821180718909</v>
+        <v>-1.2696575196507791</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26187,7 +26187,7 @@
         <v>2.9291008880836751</v>
       </c>
       <c r="C373">
-        <v>0.15301184812150659</v>
+        <v>7.9396673873173909E-2</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26198,7 +26198,7 @@
         <v>-0.17209741634783426</v>
       </c>
       <c r="C374">
-        <v>0.55818784485702244</v>
+        <v>0.24619670561701429</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26209,7 +26209,7 @@
         <v>0</v>
       </c>
       <c r="C375">
-        <v>-0.58092612510840846</v>
+        <v>-0.5700261492309745</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26220,7 +26220,7 @@
         <v>-1.846056885152366</v>
       </c>
       <c r="C376">
-        <v>0.19936461704505667</v>
+        <v>-2.5468859922751618E-2</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26231,7 +26231,7 @@
         <v>0</v>
       </c>
       <c r="C377">
-        <v>0.67101007716017991</v>
+        <v>0.71186189978686643</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26242,7 +26242,7 @@
         <v>0</v>
       </c>
       <c r="C378">
-        <v>-0.32567927220780962</v>
+        <v>-0.26920527149317136</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26253,7 +26253,7 @@
         <v>-1.2025861747401958</v>
       </c>
       <c r="C379">
-        <v>-0.21761052283581081</v>
+        <v>-0.38797806057932538</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26264,7 +26264,7 @@
         <v>0</v>
       </c>
       <c r="C380">
-        <v>0.38711651817529252</v>
+        <v>0.30523613987520565</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26275,7 +26275,7 @@
         <v>0</v>
       </c>
       <c r="C381">
-        <v>-0.12722154619642792</v>
+        <v>-0.24100241497835642</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26286,7 +26286,7 @@
         <v>-1.1459258168171547</v>
       </c>
       <c r="C382">
-        <v>-0.94612932596808264</v>
+        <v>-0.94613362937133405</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26297,7 +26297,7 @@
         <v>-1.0342398860427739</v>
       </c>
       <c r="C383">
-        <v>-0.60792004399929178</v>
+        <v>-0.74050857234325895</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26308,7 +26308,7 @@
         <v>0</v>
       </c>
       <c r="C384">
-        <v>1.3766634235878827E-2</v>
+        <v>-0.24905555118894093</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26319,7 +26319,7 @@
         <v>1.7371752631757718</v>
       </c>
       <c r="C385">
-        <v>0.27932387896775102</v>
+        <v>3.1442805393906564E-2</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="C386">
-        <v>-0.75626438279482089</v>
+        <v>-0.75299919060287801</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26341,7 +26341,7 @@
         <v>0</v>
       </c>
       <c r="C387">
-        <v>0.39033851168940426</v>
+        <v>0.42645979156544245</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26352,7 +26352,7 @@
         <v>-0.70896682648788489</v>
       </c>
       <c r="C388">
-        <v>-0.12359566509969847</v>
+        <v>-8.1826946591548808E-2</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26363,7 +26363,7 @@
         <v>0</v>
       </c>
       <c r="C389">
-        <v>8.5020900298851218E-2</v>
+        <v>0.19421528831874385</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26374,7 +26374,7 @@
         <v>0</v>
       </c>
       <c r="C390">
-        <v>-0.13294777958524961</v>
+        <v>-0.24086248561113244</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26385,7 +26385,7 @@
         <v>0</v>
       </c>
       <c r="C391">
-        <v>0.29732842982509561</v>
+        <v>0.24967111251438409</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26396,7 +26396,7 @@
         <v>0</v>
       </c>
       <c r="C392">
-        <v>0.46019512251299816</v>
+        <v>0.34182969208315556</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26407,7 +26407,7 @@
         <v>0</v>
       </c>
       <c r="C393">
-        <v>-0.50309970201602638</v>
+        <v>-0.58752657059444635</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26418,7 +26418,7 @@
         <v>1.1642658030467421</v>
       </c>
       <c r="C394">
-        <v>0.94031156796694482</v>
+        <v>1.0100348293222781</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26429,7 +26429,7 @@
         <v>0</v>
       </c>
       <c r="C395">
-        <v>0.46628184780339132</v>
+        <v>8.9564591659851783E-2</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26440,7 +26440,7 @@
         <v>0</v>
       </c>
       <c r="C396">
-        <v>0.63372555077968706</v>
+        <v>0.81027575913932115</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26451,7 +26451,7 @@
         <v>-0.85156298000507014</v>
       </c>
       <c r="C397">
-        <v>-0.20239720069658235</v>
+        <v>-0.40354481608480625</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26462,7 +26462,7 @@
         <v>0</v>
       </c>
       <c r="C398">
-        <v>0.27417123403339244</v>
+        <v>0.35389624790234947</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26473,7 +26473,7 @@
         <v>-2.5200471278343173</v>
       </c>
       <c r="C399">
-        <v>0.33579044542327502</v>
+        <v>6.8517354710753084E-2</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26484,7 +26484,7 @@
         <v>4.2237942867090617</v>
       </c>
       <c r="C400">
-        <v>0.88642776031058557</v>
+        <v>1.1070942996691469</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26495,7 +26495,7 @@
         <v>0</v>
       </c>
       <c r="C401">
-        <v>0.42532482483757006</v>
+        <v>0.17019104607497076</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26506,7 +26506,7 @@
         <v>0</v>
       </c>
       <c r="C402">
-        <v>1.1158718235414036</v>
+        <v>1.2630280881776561</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26517,7 +26517,7 @@
         <v>0</v>
       </c>
       <c r="C403">
-        <v>1.1289540656387667</v>
+        <v>1.190173182666628</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26528,7 +26528,7 @@
         <v>0</v>
       </c>
       <c r="C404">
-        <v>0.38687627734382485</v>
+        <v>0.53262973149175608</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26539,7 +26539,7 @@
         <v>0</v>
       </c>
       <c r="C405">
-        <v>-0.75931321692829579</v>
+        <v>-0.40364426688554533</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26550,7 +26550,7 @@
         <v>-0.77475983727162823</v>
       </c>
       <c r="C406">
-        <v>0.71467850287744217</v>
+        <v>0.39826958983750943</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26561,7 +26561,7 @@
         <v>-5.2910821051622605</v>
       </c>
       <c r="C407">
-        <v>-3.4678266649433942</v>
+        <v>-3.2094092687803459</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26572,7 +26572,7 @@
         <v>0</v>
       </c>
       <c r="C408">
-        <v>-1.8432256672072151</v>
+        <v>-1.5202493839036004</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26583,7 +26583,7 @@
         <v>-2.1763510720953825</v>
       </c>
       <c r="C409">
-        <v>-1.0621669138930334</v>
+        <v>-0.33077729016092233</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26594,7 +26594,7 @@
         <v>0</v>
       </c>
       <c r="C410">
-        <v>1.4126573160363636</v>
+        <v>1.8582213058533243</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26605,7 +26605,7 @@
         <v>0</v>
       </c>
       <c r="C411">
-        <v>0.15278278708018922</v>
+        <v>0.21895683468073307</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26616,7 +26616,7 @@
         <v>1.8974745602176992</v>
       </c>
       <c r="C412">
-        <v>1.8828869289159642</v>
+        <v>1.4050379643004973</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26627,7 +26627,7 @@
         <v>0</v>
       </c>
       <c r="C413">
-        <v>-0.42589609790012983</v>
+        <v>-0.62285031731009832</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26638,7 +26638,7 @@
         <v>2.9202366836520519</v>
       </c>
       <c r="C414">
-        <v>1.2385287563821028</v>
+        <v>1.1644698098704764</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26649,7 +26649,7 @@
         <v>0</v>
       </c>
       <c r="C415">
-        <v>1.4989613175711918</v>
+        <v>1.279438690534249</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26660,7 +26660,7 @@
         <v>0</v>
       </c>
       <c r="C416">
-        <v>-0.9319780434513274</v>
+        <v>-0.85273263571515057</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26671,7 +26671,7 @@
         <v>0</v>
       </c>
       <c r="C417">
-        <v>1.28506030169747</v>
+        <v>1.3004934617503865</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26682,7 +26682,7 @@
         <v>0.73431752874926925</v>
       </c>
       <c r="C418">
-        <v>0.18972450743596603</v>
+        <v>-3.9823630847421847E-2</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26693,7 +26693,7 @@
         <v>0</v>
       </c>
       <c r="C419">
-        <v>0.83622336249306362</v>
+        <v>0.86553550872049156</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26704,7 +26704,7 @@
         <v>0</v>
       </c>
       <c r="C420">
-        <v>0.20103701685253697</v>
+        <v>-2.6551374043851439E-2</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26715,7 +26715,7 @@
         <v>1.259914920926726</v>
       </c>
       <c r="C421">
-        <v>-0.7881237953759701</v>
+        <v>-0.76272021121864453</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26726,7 +26726,7 @@
         <v>0</v>
       </c>
       <c r="C422">
-        <v>5.4017010009830467E-2</v>
+        <v>-8.5614425807538849E-2</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26737,7 +26737,7 @@
         <v>0</v>
       </c>
       <c r="C423">
-        <v>-0.389652193968828</v>
+        <v>-0.4303037214078993</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26748,7 +26748,7 @@
         <v>1.5323140442491547</v>
       </c>
       <c r="C424">
-        <v>0.14431308274340426</v>
+        <v>-0.24163855223355196</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26759,7 +26759,7 @@
         <v>0</v>
       </c>
       <c r="C425">
-        <v>-6.2302498744997756E-2</v>
+        <v>-0.33459568385261063</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26770,7 +26770,7 @@
         <v>0</v>
       </c>
       <c r="C426">
-        <v>-1.3584454186173671</v>
+        <v>-1.3905096804837911</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26781,7 +26781,7 @@
         <v>0</v>
       </c>
       <c r="C427">
-        <v>0.60389921835551308</v>
+        <v>0.55893728334568982</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26792,7 +26792,7 @@
         <v>0</v>
       </c>
       <c r="C428">
-        <v>3.0068627182068455E-2</v>
+        <v>0.20862276077642805</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26803,7 +26803,7 @@
         <v>0</v>
       </c>
       <c r="C429">
-        <v>-3.487520996185136E-2</v>
+        <v>-0.14271555223555665</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26814,7 +26814,7 @@
         <v>0</v>
       </c>
       <c r="C430">
-        <v>-0.10805631063131919</v>
+        <v>-0.19718571123762568</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26825,7 +26825,7 @@
         <v>-0.47840083133406425</v>
       </c>
       <c r="C431">
-        <v>0.99832139442734469</v>
+        <v>0.82234400339055413</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26836,7 +26836,7 @@
         <v>0</v>
       </c>
       <c r="C432">
-        <v>0.22755963684619934</v>
+        <v>7.183930699796634E-2</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26847,7 +26847,7 @@
         <v>1.0678755746059396</v>
       </c>
       <c r="C433">
-        <v>0.19396218847033017</v>
+        <v>0.14052696959123426</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26858,7 +26858,7 @@
         <v>0</v>
       </c>
       <c r="C434">
-        <v>0.41860166183177028</v>
+        <v>0.22861647188308676</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26869,7 +26869,7 @@
         <v>0</v>
       </c>
       <c r="C435">
-        <v>0.25961276621044171</v>
+        <v>0.29908143439089846</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26880,7 +26880,7 @@
         <v>0</v>
       </c>
       <c r="C436">
-        <v>0.66383355858441462</v>
+        <v>0.94377910187924485</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26891,7 +26891,7 @@
         <v>0</v>
       </c>
       <c r="C437">
-        <v>0.70483565741638732</v>
+        <v>0.87952438339547234</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26902,7 +26902,7 @@
         <v>0</v>
       </c>
       <c r="C438">
-        <v>-0.77846846556089133</v>
+        <v>-0.71902999711213045</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26913,7 +26913,7 @@
         <v>1.514665157873623</v>
       </c>
       <c r="C439">
-        <v>-0.34308337214514584</v>
+        <v>-0.61152943441064855</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26924,7 +26924,7 @@
         <v>0</v>
       </c>
       <c r="C440">
-        <v>8.489989609705291E-2</v>
+        <v>-0.19289629328356753</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26935,7 +26935,7 @@
         <v>0</v>
       </c>
       <c r="C441">
-        <v>-0.99311402023338724</v>
+        <v>-0.96276773100229729</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26946,7 +26946,7 @@
         <v>0</v>
       </c>
       <c r="C442">
-        <v>0.19866222874465406</v>
+        <v>0.45681429143649371</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26957,7 +26957,7 @@
         <v>0</v>
       </c>
       <c r="C443">
-        <v>-0.3799693684243417</v>
+        <v>-0.30314949019601017</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26968,7 +26968,7 @@
         <v>0</v>
       </c>
       <c r="C444">
-        <v>0.89598341324348085</v>
+        <v>0.75540246300280922</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26979,7 +26979,7 @@
         <v>-4.9319620315560107</v>
       </c>
       <c r="C445">
-        <v>-0.47320288835369478</v>
+        <v>-0.54910087285183118</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -26990,7 +26990,7 @@
         <v>0</v>
       </c>
       <c r="C446">
-        <v>0.30470209155172218</v>
+        <v>0.12709873225994381</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27001,7 +27001,7 @@
         <v>0</v>
       </c>
       <c r="C447">
-        <v>0.13082039567743284</v>
+        <v>8.0126703473582688E-5</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27012,7 +27012,7 @@
         <v>0</v>
       </c>
       <c r="C448">
-        <v>0.54789055606201298</v>
+        <v>0.78058307073525446</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27023,7 +27023,7 @@
         <v>0</v>
       </c>
       <c r="C449">
-        <v>-0.441543842502997</v>
+        <v>-8.3412727966947944E-2</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27034,7 +27034,7 @@
         <v>0</v>
       </c>
       <c r="C450">
-        <v>-0.61237261368457441</v>
+        <v>-0.51293321341436926</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27045,7 +27045,7 @@
         <v>1.4687837009393381</v>
       </c>
       <c r="C451">
-        <v>-0.80874178508681172</v>
+        <v>-0.64462428637549885</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27056,7 +27056,7 @@
         <v>0</v>
       </c>
       <c r="C452">
-        <v>0.83872907707256472</v>
+        <v>0.72146908084174588</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27067,7 +27067,7 @@
         <v>0</v>
       </c>
       <c r="C453">
-        <v>0.82461528595810307</v>
+        <v>0.85238684275240939</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27078,7 +27078,7 @@
         <v>0</v>
       </c>
       <c r="C454">
-        <v>-3.7459115420808646E-2</v>
+        <v>0.29902063649162236</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27089,7 +27089,7 @@
         <v>0</v>
       </c>
       <c r="C455">
-        <v>-0.40931554257821617</v>
+        <v>-0.18921601620196357</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27100,7 +27100,7 @@
         <v>0</v>
       </c>
       <c r="C456">
-        <v>-0.43755140314258073</v>
+        <v>-0.3500022774525775</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27111,7 +27111,7 @@
         <v>0.97287614990324389</v>
       </c>
       <c r="C457">
-        <v>-8.2466315458630104E-2</v>
+        <v>-0.17942172239305554</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27122,7 +27122,7 @@
         <v>0</v>
       </c>
       <c r="C458">
-        <v>0.43163450451361129</v>
+        <v>0.4105482650029319</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27133,7 +27133,7 @@
         <v>0</v>
       </c>
       <c r="C459">
-        <v>3.6937000068551655E-2</v>
+        <v>0.17520765218469297</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27144,7 +27144,7 @@
         <v>0</v>
       </c>
       <c r="C460">
-        <v>-0.44991857324164702</v>
+        <v>-0.36918479632631412</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27155,7 +27155,7 @@
         <v>0</v>
       </c>
       <c r="C461">
-        <v>-0.20786111895423542</v>
+        <v>-0.18911122802048727</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27166,7 +27166,7 @@
         <v>-1.3797761858154536</v>
       </c>
       <c r="C462">
-        <v>0.1727930131480207</v>
+        <v>1.058743668138949E-2</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27177,7 +27177,7 @@
         <v>0</v>
       </c>
       <c r="C463">
-        <v>-8.3745414250210606E-2</v>
+        <v>4.8789607293030349E-2</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27188,7 +27188,7 @@
         <v>0</v>
       </c>
       <c r="C464">
-        <v>1.0315135519509857</v>
+        <v>0.84770663486542308</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27199,7 +27199,7 @@
         <v>0</v>
       </c>
       <c r="C465">
-        <v>-0.17411165832566114</v>
+        <v>-6.55397185360415E-2</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27210,7 +27210,7 @@
         <v>0</v>
       </c>
       <c r="C466">
-        <v>-6.8731785604094028E-2</v>
+        <v>-7.7911387450992325E-2</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27221,7 +27221,7 @@
         <v>0</v>
       </c>
       <c r="C467">
-        <v>-1.6143182866693726E-2</v>
+        <v>5.2777973764896763E-2</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27232,7 +27232,7 @@
         <v>0</v>
       </c>
       <c r="C468">
-        <v>-0.14298420028147882</v>
+        <v>-0.10468454615870605</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27243,7 +27243,7 @@
         <v>0.9849381860226113</v>
       </c>
       <c r="C469">
-        <v>0.45598693597216816</v>
+        <v>0.36328453699698365</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27254,7 +27254,7 @@
         <v>0</v>
       </c>
       <c r="C470">
-        <v>0.18859136648237573</v>
+        <v>0.11175652125531285</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27265,7 +27265,7 @@
         <v>0</v>
       </c>
       <c r="C471">
-        <v>0.15258311100991348</v>
+        <v>6.5812498243027304E-2</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27276,7 +27276,7 @@
         <v>0</v>
       </c>
       <c r="C472">
-        <v>-0.45013124875547633</v>
+        <v>-0.18572774641432063</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27287,7 +27287,7 @@
         <v>0</v>
       </c>
       <c r="C473">
-        <v>0.19578843646920499</v>
+        <v>7.1830437952206824E-2</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27298,7 +27298,7 @@
         <v>0</v>
       </c>
       <c r="C474">
-        <v>-0.25316370729390458</v>
+        <v>-5.0551899220516082E-2</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27309,7 +27309,7 @@
         <v>0.40759958396949203</v>
       </c>
       <c r="C475">
-        <v>0.3037952326674378</v>
+        <v>0.24587265719763812</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27320,7 +27320,7 @@
         <v>0</v>
       </c>
       <c r="C476">
-        <v>-0.32289209077800701</v>
+        <v>-0.32084470141054083</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27331,7 +27331,7 @@
         <v>0</v>
       </c>
       <c r="C477">
-        <v>-0.39305345626613769</v>
+        <v>-0.10568017598957691</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27342,7 +27342,7 @@
         <v>0</v>
       </c>
       <c r="C478">
-        <v>-3.2037140283371984E-2</v>
+        <v>-0.21023876168699698</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27353,7 +27353,7 @@
         <v>0</v>
       </c>
       <c r="C479">
-        <v>-0.58305503178325468</v>
+        <v>-0.51947767693645186</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27364,7 +27364,7 @@
         <v>-9.8063848143032413</v>
       </c>
       <c r="C480">
-        <v>-0.87244573656227631</v>
+        <v>-0.9673378898577687</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27375,7 +27375,7 @@
         <v>0</v>
       </c>
       <c r="C481">
-        <v>-1.392434428362366</v>
+        <v>-1.3907095516959793</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27386,7 +27386,7 @@
         <v>0</v>
       </c>
       <c r="C482">
-        <v>-1.3405530408031776</v>
+        <v>-1.3737911517636416</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27397,7 +27397,7 @@
         <v>0</v>
       </c>
       <c r="C483">
-        <v>1.1022966646931776</v>
+        <v>0.98387232967561844</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27408,7 +27408,7 @@
         <v>0</v>
       </c>
       <c r="C484">
-        <v>-0.24891344996896059</v>
+        <v>-0.22885549922338264</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27419,7 +27419,7 @@
         <v>0</v>
       </c>
       <c r="C485">
-        <v>0.97135624329819414</v>
+        <v>0.75503085125582914</v>
       </c>
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27430,7 +27430,7 @@
         <v>0</v>
       </c>
       <c r="C486">
-        <v>0.52805778582191409</v>
+        <v>0.65482367405250697</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27441,7 +27441,7 @@
         <v>2.3826825986483202</v>
       </c>
       <c r="C487">
-        <v>5.4271710089249033E-2</v>
+        <v>-0.25245854362517672</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27452,7 +27452,7 @@
         <v>0</v>
       </c>
       <c r="C488">
-        <v>-1.3403160511944461</v>
+        <v>-1.182491321990504</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27463,7 +27463,7 @@
         <v>0</v>
       </c>
       <c r="C489">
-        <v>-0.57264973439598277</v>
+        <v>-0.48319936824017679</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27474,7 +27474,7 @@
         <v>0</v>
       </c>
       <c r="C490">
-        <v>0.61433909953163435</v>
+        <v>0.31238846747645094</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27485,7 +27485,7 @@
         <v>0</v>
       </c>
       <c r="C491">
-        <v>3.571039679661777E-2</v>
+        <v>0.17228484984406628</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27496,7 +27496,7 @@
         <v>0</v>
       </c>
       <c r="C492">
-        <v>-0.35885623212951306</v>
+        <v>-0.51971042641782861</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27507,7 +27507,7 @@
         <v>-1.9852193941911354</v>
       </c>
       <c r="C493">
-        <v>-0.96258231023744645</v>
+        <v>-0.80381854333672476</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27518,7 +27518,7 @@
         <v>0</v>
       </c>
       <c r="C494">
-        <v>-1.2969447848146933</v>
+        <v>-1.3648801123428667</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27529,7 +27529,7 @@
         <v>0</v>
       </c>
       <c r="C495">
-        <v>-0.23811199027813976</v>
+        <v>-0.20597391569475559</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27540,7 +27540,7 @@
         <v>0</v>
       </c>
       <c r="C496">
-        <v>1.4972557035119969</v>
+        <v>1.2846518900305965</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27551,7 +27551,7 @@
         <v>0</v>
       </c>
       <c r="C497">
-        <v>-0.26729391839680439</v>
+        <v>-0.24023257490403038</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27562,7 +27562,7 @@
         <v>0</v>
       </c>
       <c r="C498">
-        <v>0.75191872658939052</v>
+        <v>0.79617524637143267</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27573,7 +27573,7 @@
         <v>0.56150101059395596</v>
       </c>
       <c r="C499">
-        <v>-0.19171711809410674</v>
+        <v>-0.26420793281011146</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27584,7 +27584,7 @@
         <v>0</v>
       </c>
       <c r="C500">
-        <v>-0.69816285098898667</v>
+        <v>-0.46832747320454621</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27595,7 +27595,7 @@
         <v>0</v>
       </c>
       <c r="C501">
-        <v>0.17161786465854134</v>
+        <v>0.10896461461657669</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27606,7 +27606,7 @@
         <v>1.4506820163291385</v>
       </c>
       <c r="C502">
-        <v>0.12008222216120555</v>
+        <v>0.16858289180895616</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27617,7 +27617,7 @@
         <v>0</v>
       </c>
       <c r="C503">
-        <v>0.89908812169012176</v>
+        <v>0.71429203170416233</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27628,7 +27628,7 @@
         <v>7.8852843788500238</v>
       </c>
       <c r="C504">
-        <v>-0.62843766876121177</v>
+        <v>-0.69935976579019066</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27639,7 +27639,7 @@
         <v>2.0177789990810355</v>
       </c>
       <c r="C505">
-        <v>0.65154889971842833</v>
+        <v>0.7009721427167952</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27650,7 +27650,7 @@
         <v>0</v>
       </c>
       <c r="C506">
-        <v>8.0941662758244326E-2</v>
+        <v>0.17215815299827067</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27661,7 +27661,7 @@
         <v>0</v>
       </c>
       <c r="C507">
-        <v>0.13399966033097499</v>
+        <v>0.26237396925947093</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27672,7 +27672,7 @@
         <v>0</v>
       </c>
       <c r="C508">
-        <v>-1.4279103192224114</v>
+        <v>-1.3451333014133746</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27683,7 +27683,7 @@
         <v>0</v>
       </c>
       <c r="C509">
-        <v>5.5417806023038016E-2</v>
+        <v>3.0925118479295813E-2</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27694,7 +27694,7 @@
         <v>-4.4323237826232695</v>
       </c>
       <c r="C510">
-        <v>-0.75550965258993541</v>
+        <v>-0.96735479878761077</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27705,7 +27705,7 @@
         <v>0</v>
       </c>
       <c r="C511">
-        <v>-0.51751075498010923</v>
+        <v>-0.41644521785301719</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27716,7 +27716,7 @@
         <v>0</v>
       </c>
       <c r="C512">
-        <v>6.1351832369459444E-2</v>
+        <v>-5.9901957869036508E-2</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27727,7 +27727,7 @@
         <v>0</v>
       </c>
       <c r="C513">
-        <v>0.26174454033356365</v>
+        <v>-1.596769585295783E-2</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27738,7 +27738,7 @@
         <v>0</v>
       </c>
       <c r="C514">
-        <v>0.25952228062222449</v>
+        <v>0.36072708026329853</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27749,7 +27749,7 @@
         <v>0</v>
       </c>
       <c r="C515">
-        <v>-0.37882087367863931</v>
+        <v>-0.42263579814174507</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27760,7 +27760,7 @@
         <v>0.19558541693422676</v>
       </c>
       <c r="C516">
-        <v>0.35514685486283654</v>
+        <v>0.17826734791434701</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27771,7 +27771,7 @@
         <v>0</v>
       </c>
       <c r="C517">
-        <v>-0.11230491019044536</v>
+        <v>-0.20407120189974928</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27782,7 +27782,7 @@
         <v>0</v>
       </c>
       <c r="C518">
-        <v>0.93093939056509245</v>
+        <v>0.75415926906024922</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27793,7 +27793,7 @@
         <v>0</v>
       </c>
       <c r="C519">
-        <v>-0.28978690988491013</v>
+        <v>-0.34816937855841323</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27804,7 +27804,7 @@
         <v>0</v>
       </c>
       <c r="C520">
-        <v>-0.28621049025829948</v>
+        <v>-8.5913562153513492E-2</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27815,7 +27815,7 @@
         <v>0</v>
       </c>
       <c r="C521">
-        <v>0.19107130393970642</v>
+        <v>0.31918627853668036</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27826,7 +27826,7 @@
         <v>0</v>
       </c>
       <c r="C522">
-        <v>0.69128289088863459</v>
+        <v>0.55310728091962502</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27837,7 +27837,7 @@
         <v>-0.43298026755116631</v>
       </c>
       <c r="C523">
-        <v>-0.81995762250636794</v>
+        <v>-0.7355856322447939</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27848,7 +27848,7 @@
         <v>0</v>
       </c>
       <c r="C524">
-        <v>0.50768841857552427</v>
+        <v>0.55132953062627243</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27859,7 +27859,7 @@
         <v>0</v>
       </c>
       <c r="C525">
-        <v>-0.20443600277909185</v>
+        <v>-0.19346637615158391</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27870,7 +27870,7 @@
         <v>0</v>
       </c>
       <c r="C526">
-        <v>0.34480223757879697</v>
+        <v>0.58592846812955635</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27881,7 +27881,7 @@
         <v>0</v>
       </c>
       <c r="C527">
-        <v>0.3249734659461837</v>
+        <v>0.22303224540765323</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27892,7 +27892,7 @@
         <v>0</v>
       </c>
       <c r="C528">
-        <v>-1.7845214605339053</v>
+        <v>-1.5038914690583227</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27903,7 +27903,7 @@
         <v>2.0508602109186365</v>
       </c>
       <c r="C529">
-        <v>-0.50692855358120903</v>
+        <v>-0.37882755879112356</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27914,7 +27914,7 @@
         <v>0</v>
       </c>
       <c r="C530">
-        <v>0.51302761498565408</v>
+        <v>0.49194314845252501</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27925,7 +27925,7 @@
         <v>0</v>
       </c>
       <c r="C531">
-        <v>0.29779163889237414</v>
+        <v>0.22402264130270289</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27936,7 +27936,7 @@
         <v>0</v>
       </c>
       <c r="C532">
-        <v>3.4269081363466555E-2</v>
+        <v>-9.1599629475171085E-2</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27947,7 +27947,7 @@
         <v>0</v>
       </c>
       <c r="C533">
-        <v>0.55751550417005735</v>
+        <v>0.46654319936882849</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27958,7 +27958,7 @@
         <v>0</v>
       </c>
       <c r="C534">
-        <v>-0.85984142522595286</v>
+        <v>-0.82786998427400627</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="C535">
-        <v>-0.79002638642285683</v>
+        <v>-0.41577753183725946</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27980,7 +27980,7 @@
         <v>-4.2671075877589022</v>
       </c>
       <c r="C536">
-        <v>0.62191285597826562</v>
+        <v>0.38161135018801373</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -27991,7 +27991,7 @@
         <v>0</v>
       </c>
       <c r="C537">
-        <v>-0.68000621000669914</v>
+        <v>-0.40819397488995068</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28002,7 +28002,7 @@
         <v>0</v>
       </c>
       <c r="C538">
-        <v>0.60329290917425027</v>
+        <v>0.42991013981100801</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28013,7 +28013,7 @@
         <v>0</v>
       </c>
       <c r="C539">
-        <v>-0.15219394097380315</v>
+        <v>-0.18060113884763807</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28024,7 +28024,7 @@
         <v>0</v>
       </c>
       <c r="C540">
-        <v>0.37852369993695273</v>
+        <v>0.54600915221968793</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28035,7 +28035,7 @@
         <v>1.0688466057140333</v>
       </c>
       <c r="C541">
-        <v>0.480402061544206</v>
+        <v>0.36650183169733219</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28046,7 +28046,7 @@
         <v>0</v>
       </c>
       <c r="C542">
-        <v>-0.39138403619594875</v>
+        <v>1.0527992955230807</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28057,7 +28057,7 @@
         <v>0</v>
       </c>
       <c r="C543">
-        <v>-1.3891279016499969</v>
+        <v>-1.0550630275484321</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28068,7 +28068,7 @@
         <v>-8.0195718951551651</v>
       </c>
       <c r="C544">
-        <v>-2.0940756501353959</v>
+        <v>-1.7812014986134781</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28079,7 +28079,7 @@
         <v>3.0496930969031695</v>
       </c>
       <c r="C545">
-        <v>1.1876685827572961</v>
+        <v>1.2107313651537528</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28090,7 +28090,7 @@
         <v>0</v>
       </c>
       <c r="C546">
-        <v>1.2159676286063332</v>
+        <v>0.97286263604263101</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28101,7 +28101,7 @@
         <v>-3.1670359574793312</v>
       </c>
       <c r="C547">
-        <v>-0.87492790087678918</v>
+        <v>-0.65811318301481747</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28112,7 +28112,7 @@
         <v>0</v>
       </c>
       <c r="C548">
-        <v>-4.0965840858722444E-2</v>
+        <v>-0.1765912788134166</v>
       </c>
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28123,7 +28123,7 @@
         <v>0</v>
       </c>
       <c r="C549">
-        <v>-0.55744395625278564</v>
+        <v>-0.55210248365866599</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28134,7 +28134,7 @@
         <v>0</v>
       </c>
       <c r="C550">
-        <v>-0.26649475907985698</v>
+        <v>-0.47912157510195741</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28145,7 +28145,7 @@
         <v>0</v>
       </c>
       <c r="C551">
-        <v>-0.66447242774398674</v>
+        <v>-0.27288730123168609</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28156,7 +28156,7 @@
         <v>0</v>
       </c>
       <c r="C552">
-        <v>0.22566767136013816</v>
+        <v>-7.9762105023474916E-2</v>
       </c>
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28167,7 +28167,7 @@
         <v>0.54199757341829269</v>
       </c>
       <c r="C553">
-        <v>3.387205640567529E-2</v>
+        <v>-1.7752493754434641E-4</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28178,7 +28178,7 @@
         <v>3.8748170317390596</v>
       </c>
       <c r="C554">
-        <v>-0.71292017588087309</v>
+        <v>-0.53543863972609307</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28189,7 +28189,7 @@
         <v>0</v>
       </c>
       <c r="C555">
-        <v>0.63057840995301517</v>
+        <v>0.27062933116972948</v>
       </c>
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28200,7 +28200,7 @@
         <v>3.5176987694000772</v>
       </c>
       <c r="C556">
-        <v>0.16170710405189245</v>
+        <v>0.38386800117381858</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28211,7 +28211,7 @@
         <v>5.944596461021554</v>
       </c>
       <c r="C557">
-        <v>0.57682995416398808</v>
+        <v>0.54043298888701008</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28222,7 +28222,7 @@
         <v>0</v>
       </c>
       <c r="C558">
-        <v>0.25671510518940766</v>
+        <v>0.84138048037470448</v>
       </c>
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28233,7 +28233,7 @@
         <v>2.2696484826095253</v>
       </c>
       <c r="C559">
-        <v>0.65586267208883453</v>
+        <v>0.49031322556059365</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28244,7 +28244,7 @@
         <v>-9.8821588358829278</v>
       </c>
       <c r="C560">
-        <v>-0.19940385849783634</v>
+        <v>0.15733914659639561</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28255,7 +28255,7 @@
         <v>0</v>
       </c>
       <c r="C561">
-        <v>-0.54769394132538307</v>
+        <v>-0.4359788634069986</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28266,7 +28266,7 @@
         <v>0.41814841808172643</v>
       </c>
       <c r="C562">
-        <v>1.2353245864659745</v>
+        <v>1.296534646098916</v>
       </c>
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28277,7 +28277,7 @@
         <v>2.3383195590996859</v>
       </c>
       <c r="C563">
-        <v>0.79968279564215383</v>
+        <v>0.96783085882601272</v>
       </c>
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28288,7 +28288,7 @@
         <v>-1.0324059454352004</v>
       </c>
       <c r="C564">
-        <v>-0.35994892288287172</v>
+        <v>-0.42498050989321068</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28299,7 +28299,7 @@
         <v>1.684757923174929</v>
       </c>
       <c r="C565">
-        <v>-0.34051413390579188</v>
+        <v>-0.21729719731121785</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28310,7 +28310,7 @@
         <v>1.4765266477553718</v>
       </c>
       <c r="C566">
-        <v>1.2238247085078036</v>
+        <v>0.83347851074493018</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28321,7 +28321,7 @@
         <v>0.62810663668492583</v>
       </c>
       <c r="C567">
-        <v>0.15609061977106611</v>
+        <v>0.33715660583548895</v>
       </c>
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28332,7 +28332,7 @@
         <v>0.97863322546901088</v>
       </c>
       <c r="C568">
-        <v>1.0687831693200187</v>
+        <v>1.1262549950876453</v>
       </c>
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28343,7 +28343,7 @@
         <v>0</v>
       </c>
       <c r="C569">
-        <v>-1.141035186163774</v>
+        <v>-0.58169966414187002</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28354,7 +28354,7 @@
         <v>0.44353812821332345</v>
       </c>
       <c r="C570">
-        <v>1.0224595892941915</v>
+        <v>0.9077704865877354</v>
       </c>
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28365,7 +28365,7 @@
         <v>-2.1602537733453833</v>
       </c>
       <c r="C571">
-        <v>0.72603657495021445</v>
+        <v>0.43544620064786116</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28376,7 +28376,7 @@
         <v>0</v>
       </c>
       <c r="C572">
-        <v>-1.4674877386332617</v>
+        <v>-1.5419790971131737</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28387,7 +28387,7 @@
         <v>-2.9224307249801051</v>
       </c>
       <c r="C573">
-        <v>-0.36195413669617432</v>
+        <v>-0.53205240299274603</v>
       </c>
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28398,7 +28398,7 @@
         <v>0.53441254544771888</v>
       </c>
       <c r="C574">
-        <v>-0.62370125891947492</v>
+        <v>-0.40411264347187742</v>
       </c>
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28409,7 +28409,7 @@
         <v>2.4412022204702972</v>
       </c>
       <c r="C575">
-        <v>0.51002170092392318</v>
+        <v>0.60379560629322648</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28420,7 +28420,7 @@
         <v>0</v>
       </c>
       <c r="C576">
-        <v>-6.3061898427076449E-2</v>
+        <v>-0.44650720642112668</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28431,7 +28431,7 @@
         <v>-2.8964984035688834</v>
       </c>
       <c r="C577">
-        <v>-0.6800003483013547</v>
+        <v>-0.65265639626071748</v>
       </c>
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28442,7 +28442,7 @@
         <v>0</v>
       </c>
       <c r="C578">
-        <v>-2.6307092007274804E-3</v>
+        <v>2.281607715230332E-2</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28453,7 +28453,7 @@
         <v>0</v>
       </c>
       <c r="C579">
-        <v>9.9208305752599715E-2</v>
+        <v>-0.23693111986071308</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28464,7 +28464,7 @@
         <v>0</v>
       </c>
       <c r="C580">
-        <v>-0.60598414119154087</v>
+        <v>-0.54723841342701873</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28475,7 +28475,7 @@
         <v>0</v>
       </c>
       <c r="C581">
-        <v>0.48973026706155615</v>
+        <v>0.65702489135313624</v>
       </c>
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28486,7 +28486,7 @@
         <v>0</v>
       </c>
       <c r="C582">
-        <v>-0.98182445941055918</v>
+        <v>-1.0542290967998782</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28497,7 +28497,7 @@
         <v>0.44169294304720064</v>
       </c>
       <c r="C583">
-        <v>0.43284863356739195</v>
+        <v>0.37555819979799554</v>
       </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28508,7 +28508,7 @@
         <v>0</v>
       </c>
       <c r="C584">
-        <v>0.10145516607164837</v>
+        <v>0.10264827110028253</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28519,7 +28519,7 @@
         <v>0</v>
       </c>
       <c r="C585">
-        <v>0.57838399298990628</v>
+        <v>0.34150108305118787</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28530,7 +28530,7 @@
         <v>0</v>
       </c>
       <c r="C586">
-        <v>0.50763807696729057</v>
+        <v>0.70296298591416129</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28541,7 +28541,7 @@
         <v>0</v>
       </c>
       <c r="C587">
-        <v>-0.17637956332269869</v>
+        <v>-0.15926517468573995</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28552,7 +28552,7 @@
         <v>-2.4830796560787278</v>
       </c>
       <c r="C588">
-        <v>-0.62402007538018922</v>
+        <v>-0.58020737543538026</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28563,7 +28563,7 @@
         <v>0</v>
       </c>
       <c r="C589">
-        <v>6.1835249706912308E-2</v>
+        <v>3.9127218436281447E-2</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28574,7 +28574,7 @@
         <v>0</v>
       </c>
       <c r="C590">
-        <v>1.0631864607025088</v>
+        <v>1.2177399762561889</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28585,7 +28585,7 @@
         <v>0</v>
       </c>
       <c r="C591">
-        <v>-5.7665907418474133E-2</v>
+        <v>-2.9998041809238978E-2</v>
       </c>
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28596,7 +28596,7 @@
         <v>-0.25207540531636619</v>
       </c>
       <c r="C592">
-        <v>0.42607690255337582</v>
+        <v>0.63434898691724273</v>
       </c>
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28607,7 +28607,7 @@
         <v>0</v>
       </c>
       <c r="C593">
-        <v>0.16991132430826342</v>
+        <v>0.37719282374458846</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28618,7 +28618,7 @@
         <v>0</v>
       </c>
       <c r="C594">
-        <v>-0.84536951974652796</v>
+        <v>-0.84933299343752156</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28629,7 +28629,7 @@
         <v>-3.0369352737144646</v>
       </c>
       <c r="C595">
-        <v>-0.17180775298320383</v>
+        <v>-6.5558577283837448E-3</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28640,7 +28640,7 @@
         <v>0</v>
       </c>
       <c r="C596">
-        <v>0.36302425492015128</v>
+        <v>0.15289034492731624</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28651,7 +28651,7 @@
         <v>0</v>
       </c>
       <c r="C597">
-        <v>-0.75987258619286346</v>
+        <v>-0.45904897151805923</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28662,7 +28662,7 @@
         <v>0.52963527533619992</v>
       </c>
       <c r="C598">
-        <v>-0.12103108831020595</v>
+        <v>2.3944912360420738E-3</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28673,7 +28673,7 @@
         <v>0</v>
       </c>
       <c r="C599">
-        <v>0.27159830559941706</v>
+        <v>0.23737867144441865</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28684,7 +28684,7 @@
         <v>2.4411166968157234</v>
       </c>
       <c r="C600">
-        <v>-0.12546774481645745</v>
+        <v>-8.2365219964076308E-2</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28695,7 +28695,7 @@
         <v>0.13195504789345275</v>
       </c>
       <c r="C601">
-        <v>-7.4233139931096856E-2</v>
+        <v>1.1997744335305772E-2</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28706,7 +28706,7 @@
         <v>0</v>
       </c>
       <c r="C602">
-        <v>0.22748917420546641</v>
+        <v>0.7531442491620105</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28717,7 +28717,7 @@
         <v>0</v>
       </c>
       <c r="C603">
-        <v>0.22183213585575007</v>
+        <v>-0.88220696685871225</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28728,7 +28728,7 @@
         <v>-1.2044859613614753</v>
       </c>
       <c r="C604">
-        <v>0.44410811373235909</v>
+        <v>-5.7495972773478385E-2</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28739,7 +28739,7 @@
         <v>-6.2420925974473853</v>
       </c>
       <c r="C605">
-        <v>0.16142767870687469</v>
+        <v>-0.57227703900126359</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28750,7 +28750,7 @@
         <v>2.4495729338091987</v>
       </c>
       <c r="C606">
-        <v>-0.17882935294980271</v>
+        <v>-9.8034627584121403E-2</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28761,7 +28761,7 @@
         <v>0</v>
       </c>
       <c r="C607">
-        <v>0.19382557046175342</v>
+        <v>0.66345079357228487</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28772,7 +28772,7 @@
         <v>1.1611236084589465</v>
       </c>
       <c r="C608">
-        <v>0.33781906778553666</v>
+        <v>-0.25959949589033032</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28783,7 +28783,7 @@
         <v>-0.51205738943307832</v>
       </c>
       <c r="C609">
-        <v>0.13210805874268855</v>
+        <v>0.32513277563753057</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28794,7 +28794,7 @@
         <v>0.96784731000360569</v>
       </c>
       <c r="C610">
-        <v>-7.7336304582164547E-2</v>
+        <v>4.3127140680198656E-2</v>
       </c>
     </row>
     <row r="611" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28805,7 +28805,7 @@
         <v>1.3729077319203784</v>
       </c>
       <c r="C611">
-        <v>0.52480430824112345</v>
+        <v>4.2624645799940346E-2</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28816,7 +28816,7 @@
         <v>0.5918510003004559</v>
       </c>
       <c r="C612">
-        <v>-0.42851720224311157</v>
+        <v>-0.37801611150638031</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -28827,7 +28827,7 @@
         <v>1.4648009173008574</v>
       </c>
       <c r="C613">
-        <v>0.13565719299972115</v>
+        <v>-0.33625167740064699</v>
       </c>
     </row>
   </sheetData>
